--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0028.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0028.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng giật sét một Discord trong phạm vi, gây Electro DMG.</t>
+          <t>Thỉnh thoảng giật sét một Tacet Discord trong phạm vi, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Glacio DMG trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Sát Thương Glacio trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Glacio DMG trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Sát Thương Glacio trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Glacio DMG trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Sát Thương Glacio trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Glacio DMG trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Sát Thương Glacio trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Glacio DMG trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Sát Thương Glacio trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu Dodgem xu xuống dưới, gây Fusion DMG. Tacet Discord bị tiêu diệt bởi thiết bị có thể nhận được Xu May Mắn.</t>
+          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu ném xu xuống dưới, gây Sát Thương Fusion. Tacet Discord bị tiêu diệt bởi thiết bị có thể nhận được Xu May Mắn.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu Dodgem xu xuống dưới, gây Fusion DMG. Tacet Discord bị tiêu diệt bởi thiết bị có thể nhận được Xu May Mắn.</t>
+          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu ném xu xuống dưới, gây Sát Thương Fusion. Tacet Discord bị tiêu diệt bởi thiết bị có thể nhận được Xu May Mắn.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu Dodgem xu xuống dưới, gây Fusion DMG. Tacet Discord bị tiêu diệt bởi thiết bị có thể nhận được Xu May Mắn.</t>
+          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu ném xu xuống dưới, gây Sát Thương Fusion. Tacet Discord bị tiêu diệt bởi thiết bị có thể nhận được Xu May Mắn.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu Dodgem xu xuống dưới, gây Fusion DMG. Tacet Discord bị tiêu diệt bởi thiết bị có thể nhận được Xu May Mắn.</t>
+          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu ném xu xuống dưới, gây Sát Thương Fusion. Tacet Discord bị tiêu diệt bởi thiết bị có thể nhận được Xu May Mắn.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu Dodgem xu xuống dưới, gây Fusion DMG. Tacet Discord bị tiêu diệt bởi thiết bị có thể nhận được Xu May Mắn.</t>
+          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu ném xu xuống dưới, gây Sát Thương Fusion. Tacet Discord bị tiêu diệt bởi thiết bị có thể nhận được Xu May Mắn.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp) và bắn vào Tacet Discord đi qua, gây Fusion DMG cho mục tiêu trong phạm vi.</t>
+          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp) và bắn vào Tacet Discord đi qua, gây Sát Thương Fusion cho mục tiêu trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp) và bắn vào Tacet Discord đi qua, gây Fusion DMG cho mục tiêu trong phạm vi.</t>
+          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp) và bắn vào Tacet Discord đi qua, gây Sát Thương Fusion cho mục tiêu trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp) và bắn vào Tacet Discord đi qua, gây Fusion DMG cho mục tiêu trong phạm vi.</t>
+          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp) và bắn vào Tacet Discord đi qua, gây Sát Thương Fusion cho mục tiêu trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp) và bắn vào Tacet Discord đi qua, gây Fusion DMG cho mục tiêu trong phạm vi.</t>
+          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp) và bắn vào Tacet Discord đi qua, gây Sát Thương Fusion cho mục tiêu trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp) và bắn vào Tacet Discord đi qua, gây Fusion DMG cho mục tiêu trong phạm vi.</t>
+          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp) và bắn vào Tacet Discord đi qua, gây Sát Thương Fusion cho mục tiêu trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Physical lên Tacet Discord.</t>
+          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Vật Lý lên Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Physical lên Tacet Discord.</t>
+          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Vật Lý lên Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Physical lên Tacet Discord.</t>
+          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Vật Lý lên Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Tacetite Spikes gây thêm &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; Sát Thương và chuyển thành Electro DMG.</t>
+          <t>Gai Tổ Tacet gây thêm &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; Sát Thương và chuyển thành Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Tacetite Spikes gây thêm &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; Sát Thương và chuyển thành Glacio DMG.</t>
+          <t>Gai Tổ Tacet gây thêm &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; Sát Thương và chuyển thành Sát Thương Glacio.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Fusion DMG lên các Tacet Discord phía trước.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Sát Thương Fusion lên các Tacet Discord phía trước.</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Fusion DMG lên các Tacet Discord phía trước.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Sát Thương Fusion lên các Tacet Discord phía trước.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Fusion DMG lên các Tacet Discord phía trước.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Sát Thương Fusion lên các Tacet Discord phía trước.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Hơi thở của Drake Echoes thiêu đốt mục tiêu, gây &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; Fusion DMG theo thời gian.</t>
+          <t>Hơi thở của Drake Echoes thiêu đốt mục tiêu, gây &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; Sát Thương Fusion theo thời gian.</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Tất cả Kháng của Tacet Discord bị ảnh hưởng bởi Glacio Beacon đều giảm &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;.</t>
+          <t>Tất cả Kháng của Tacet Discord bị ảnh hưởng bởi Đèn Hiệu Glacio đều giảm &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Sốc Điện gây thêm &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; sát thương.</t>
+          <t>Sốc Điện gây thêm &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; DMG.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Nhiễm Lỗi gây &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; Sát Thương Physical.</t>
+          <t>Nhiễm Lỗi gây &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; Sát Thương Vật Lý.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Physical diện rộng.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Vật Lý diện rộng.</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Physical diện rộng.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Vật Lý diện rộng.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Physical diện rộng.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Vật Lý diện rộng.</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Junrock Echo giờ gây Glacio DMG và làm chậm mục tiêu &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;.</t>
+          <t>Junrock Echo giờ gây Sát Thương Glacio và làm chậm mục tiêu &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Electro DMG.</t>
+          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Electro DMG.</t>
+          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Electro DMG.</t>
+          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Thương Sét gây &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; sát thương ít hơn, nhưng giờ thiết bị bắn ra 2 Thương Sét cùng lúc.</t>
+          <t>Thương Sét gây &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; DMG ít hơn, nhưng giờ thiết bị bắn ra 2 Thương Sét cùng lúc.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Khi Tacet Discord đến gần, bắn mảnh Echo gây Sát Thương Physical lên mục tiêu phía trước.</t>
+          <t>Khi Tacet Discord đến gần, bắn mảnh Tổ Tacet gây Sát Thương Vật Lý lên mục tiêu phía trước.</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Khi Tacet Discord đến gần, bắn mảnh Echo gây Sát Thương Physical lên mục tiêu phía trước.</t>
+          <t>Khi Tacet Discord đến gần, bắn mảnh Tổ Tacet gây Sát Thương Vật Lý lên mục tiêu phía trước.</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Khi Tacet Discord đến gần, bắn mảnh Echo gây Sát Thương Physical lên mục tiêu phía trước.</t>
+          <t>Khi Tacet Discord đến gần, bắn mảnh Tổ Tacet gây Sát Thương Vật Lý lên mục tiêu phía trước.</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Mảnh Echo giờ gây Fusion DMG và Thiêu Đốt mục tiêu, gây &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; Fusion DMG theo thời gian.</t>
+          <t>Mảnh Tổ Tacet giờ gây Sát Thương Fusion và Thiêu Đốt mục tiêu, gây &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; Sát Thương Fusion theo thời gian.</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Mỗi khi bắn mảnh Tacetite, có xác suất &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; gây thêm &lt;color=#fde7a1ff&gt;{1}&lt;/color&gt; sát thương.</t>
+          <t>Mỗi khi bắn mảnh Tacetite, có xác suất &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; gây thêm &lt;color=#fde7a1ff&gt;{1}&lt;/color&gt; DMG.</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Khí áp suất cao giờ gây Aero DMG và xóa bỏ Ô Nhiễm Tần Số trong phạm vi.</t>
+          <t>Khí áp suất cao giờ gây DMG Aero và xóa bỏ Ô Nhiễm Tần Số trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Giờ đây, xoáy nhân tạo sẽ gây Aero DMG và loại bỏ Tàng Hình của Tacet Discord.</t>
+          <t>Giờ đây, xoáy nhân tạo sẽ gây Sát Thương Aero và loại bỏ Tàng Hình của Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Physical và đẩy lùi Tacet Discord trên đường đi.</t>
+          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Vật Lý và đẩy lùi Tacet Discord trên đường đi.</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Physical và đẩy lùi Tacet Discord trên đường đi.</t>
+          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Vật Lý và đẩy lùi Tacet Discord trên đường đi.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Physical và đẩy lùi Tacet Discord trên đường đi.</t>
+          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Vật Lý và đẩy lùi Tacet Discord trên đường đi.</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Hồi Âm Hoartoise gây thêm &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; sát thương và giờ gây sát thương Hệ Fusion.</t>
+          <t>Hồi Âm Hoartoise gây thêm &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; DMG và giờ gây DMG Hệ Fusion.</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng giật sét một Discord trong phạm vi, gây Electro DMG.</t>
+          <t>Thỉnh thoảng giật sét một Tacet Discord trong phạm vi, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng giật sét một Discord trong phạm vi, gây Electro DMG.</t>
+          <t>Thỉnh thoảng giật sét một Tacet Discord trong phạm vi, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng giật sét một Discord trong phạm vi, gây Electro DMG.</t>
+          <t>Thỉnh thoảng giật sét một Tacet Discord trong phạm vi, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Tiêu diệt mục tiêu bằng sốc điện sẽ tạo ra một cơn bão sét ngay tại chỗ, gây &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; Electro DMG.</t>
+          <t>Tiêu diệt mục tiêu bằng sốc điện sẽ tạo ra một cơn bão sét ngay tại chỗ, gây &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Xoáy nước không còn loại bỏ Shield nữa mà khiến các Tacet Discord lơ lửng chịu thêm &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; Sát Thương.</t>
+          <t>Xoáy nước không còn loại bỏ Khiên nữa mà khiến các Tacet Discord lơ lửng chịu thêm &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Glacio DMG trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Sát Thương Glacio trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Glacio DMG trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Sát Thương Glacio trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Glacio DMG trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Sát Thương Glacio trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu Dodgem xu xuống dưới, gây Fusion DMG. Tacet Discord bị tiêu diệt bởi thiết bị có &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;% cơ hội rơi Xu May Mắn.</t>
+          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu ném xu xuống dưới, gây Sát Thương Fusion. Tacet Discord bị tiêu diệt bởi thiết bị có &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;% cơ hội rơi Xu May Mắn.</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu Dodgem xu xuống dưới, gây Fusion DMG. Tacet Discord bị tiêu diệt bởi thiết bị có &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;% cơ hội rơi Xu May Mắn.</t>
+          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu ném xu xuống dưới, gây Sát Thương Fusion. Tacet Discord bị tiêu diệt bởi thiết bị có &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;% cơ hội rơi Xu May Mắn.</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu Dodgem xu xuống dưới, gây Fusion DMG. Tacet Discord bị tiêu diệt bởi thiết bị có &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;% cơ hội rơi Xu May Mắn.</t>
+          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu ném xu xuống dưới, gây Sát Thương Fusion. Tacet Discord bị tiêu diệt bởi thiết bị có &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;% cơ hội rơi Xu May Mắn.</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Khi Discord bị Thiêu Đốt, Chest Mimic sẽ giảm Fusion RES của nó &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; trong &lt;color=#fde7a1ff&gt;{1}&lt;/color&gt; giây khi trúng đòn.</t>
+          <t>Khi Tacet Discord bị Thiêu Đốt, Chest Mimic sẽ giảm Kháng Fusion của nó &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; trong &lt;color=#fde7a1ff&gt;{1}&lt;/color&gt; giây khi trúng đòn.</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Chest Mimic gây thêm &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; sát thương.</t>
+          <t>Rương Biến Hình gây thêm &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt; DMG.</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;) và bắn vào Tacet Discord đi qua, gây Fusion DMG cho mục tiêu trong phạm vi.</t>
+          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;) và bắn vào Tacet Discord đi qua, gây Sát Thương Fusion cho mục tiêu trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;) và bắn vào Tacet Discord đi qua, gây Fusion DMG cho mục tiêu trong phạm vi.</t>
+          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;) và bắn vào Tacet Discord đi qua, gây Sát Thương Fusion cho mục tiêu trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;) và bắn vào Tacet Discord đi qua, gây Fusion DMG cho mục tiêu trong phạm vi.</t>
+          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;) và bắn vào Tacet Discord đi qua, gây Sát Thương Fusion cho mục tiêu trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Physical DMG</t>
+          <t>DMG Vật lý</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Dùng để tạo xung sốc, gây Sát Thương Physical cao cho Tacet Discord trong phạm vi nhất định.</t>
+          <t>Dùng để tạo xung sốc, gây Sát Thương Vật Lý cao cho Tacet Discord trong phạm vi nhất định.</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Dùng để phục hồi một lượng nhỏ Độ Bền Energy Matrix</t>
+          <t>Dùng để phục hồi một lượng nhỏ Độ Bền Ma Trận Năng Lượng</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Dùng để tăng cường Vũ Khí của KU-Roro, gia tăng đáng kể sức Tấn Công trong một khoảng thời gian nhất định.</t>
+          <t>Dùng để tăng cường Vũ Khí của KU-Roro, gia tăng đáng kể sức ATK trong một khoảng thời gian nhất định.</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Dùng để tăng cường tất cả Combat Machines gần đó, gia tăng Attack và Attack Speed trong một khoảng thời gian nhất định.</t>
+          <t>Dùng để tăng cường tất cả Máy Chiến Đấu gần đó, gia tăng ATK và Tốc Độ ATK trong một khoảng thời gian nhất định.</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Dùng để tạo xung diện rộng, gây Fusion DMG cao cho Tacet Discord trong phạm vi.</t>
+          <t>Dùng để tạo xung diện rộng, gây Sát Thương Fusion cao cho Tacet Discord trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Dùng để phục hồi một lượng lớn Độ Bền Energy Matrix</t>
+          <t>Dùng để phục hồi một lượng lớn Độ Bền Ma Trận Năng Lượng</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Tăng cường DMG Thiết bị I</t>
+          <t>Tăng cường Sát thương Thiết bị I</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Tăng cường DMG Thiết bị II</t>
+          <t>Tăng cường Sát thương Thiết bị II</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Speed Shooter và Plasma Cannon gây thêm &lt;color=#fde7a1ff&gt;40%&lt;/color&gt; sát thương.</t>
+          <t>Xạ Thủ Tốc Độ và Pháo Plasma gây thêm &lt;color=#fde7a1ff&gt;40%&lt;/color&gt; DMG.</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Cooldown chiêu của Repulsion Field và Trường Trì Trệ giảm &lt;color=#fde7a1ff&gt;30%&lt;/color&gt;.</t>
+          <t>Thời gian hồi chiêu của Trường Đẩy Lùi và Trường Trì Trệ giảm &lt;color=#fde7a1ff&gt;30%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Crit. Rate của Combat Machines tăng &lt;color=#fde7a1ff&gt;20%&lt;/color&gt;.</t>
+          <t>Crit. Rate của Máy Chiến Đấu tăng &lt;color=#fde7a1ff&gt;20%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Cooldown chiêu của Combat Machines giảm &lt;color=#fde7a1ff&gt;10%&lt;/color&gt;.</t>
+          <t>Thời gian hồi chiêu của Máy Chiến Đấu giảm &lt;color=#fde7a1ff&gt;10%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Tấn Công của Combat Machines tăng &lt;color=#fde7a1ff&gt;4%&lt;/color&gt;.</t>
+          <t>ATK của Máy Chiến Đấu tăng &lt;color=#fde7a1ff&gt;4%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Crit. DMG của Combat Machines tăng &lt;color=#fde7a1ff&gt;20%&lt;/color&gt;.</t>
+          <t>Crit. DMG của Máy Chiến Đấu tăng &lt;color=#fde7a1ff&gt;20%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Tấn Công của Combat Machines tăng &lt;color=#fde7a1ff&gt;6%&lt;/color&gt;.</t>
+          <t>ATK của Máy Chiến Đấu tăng &lt;color=#fde7a1ff&gt;6%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Crit. DMG của Combat Machines tăng &lt;color=#fde7a1ff&gt;30%&lt;/color&gt;.</t>
+          <t>Crit. DMG của Máy Chiến Đấu tăng &lt;color=#fde7a1ff&gt;30%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Sau khi vượt qua làn sóng Tacet Discord thứ 7, các kẻ địch từ Wave 7 sẽ xuất hiện trong tất cả các làn sóng tiếp theo.</t>
+          <t>Sau khi vượt qua làn sóng Tacet Discord thứ 7, các kẻ địch từ Làn sóng 7 sẽ xuất hiện trong tất cả các làn sóng tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Sau khi vượt qua làn sóng Tacet Discord thứ 19, các kẻ địch từ Wave 15-19 sẽ xuất hiện trong tất cả các làn sóng tiếp theo.</t>
+          <t>Sau khi vượt qua làn sóng Tacet Discord thứ 19, các kẻ địch từ Làn sóng 15-19 sẽ xuất hiện trong tất cả các làn sóng tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Kịch Bản Mô Phỏng: Đàn Tacet Discord đang cố vượt cầu tấn công dân thường chưa kịp sơ tán. Giữ vững phòng tuyến và tiêu diệt mọi kẻ địch xuất hiện.</t>
+          <t>Kịch Bản Mô Phỏng: Hordes of Tacet Discords are attempting to cross the bridge and attack civilians who have yet to be evacuated. Hold the line and eliminate all enemies on sight.</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Chương: Đội đặc nhiệm đã khống chế thành công mục tiêu. Hãy chặn đứng đợt tấn công cuối của Tacet Discord cho đến khi đội rút về khu vực an toàn.</t>
+          <t>Chương: The special operation squad has successfully contained the target. Hold back the final waves of Tacet Discords until the squad evacuates to a safe zone.</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Mức Đe Dọa Tăng Cao: Matrix Durability Tối Đa giảm xuống còn &lt;color=#fde7a1ff&gt;15&lt;/color&gt;.
+          <t>Mức Đe Dọa Tăng Cao: Độ Bền Ma Trận Tối Đa giảm xuống còn &lt;color=#fde7a1ff&gt;15&lt;/color&gt;.
 Tacet Discord có lượng HP cao hơn.
 Địa hình được mở rộng trong mô phỏng này.</t>
         </is>
@@ -7277,8 +7277,8 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Mức Đe Dọa Tăng: Matrix Durability Tối Đa giảm xuống còn &lt;color=#fde7a1ff&gt;15&lt;/color&gt;. Bắt đầu với thêm &lt;color=#fde7a1ff&gt;1000&lt;/color&gt; Tín Dụng Mô Phỏng.
-Combat Machines Loại Electro gây thêm &lt;color=#fde7a1ff&gt;20%&lt;/color&gt; sát thương và Crit. DMG tăng &lt;color=#fde7a1ff&gt;50%&lt;/color&gt;.
+          <t>Mức Đe Dọa Tăng: Độ Bền Ma Trận Tối Đa giảm xuống còn &lt;color=#fde7a1ff&gt;15&lt;/color&gt;. Bắt đầu với thêm &lt;color=#fde7a1ff&gt;1000&lt;/color&gt; Tín Dụng Mô Phỏng.
+Máy Chiến Đấu Loại Electro gây thêm &lt;color=#fde7a1ff&gt;20%&lt;/color&gt; DMG và Crit. DMG tăng &lt;color=#fde7a1ff&gt;50%&lt;/color&gt;.
 Hiệu ứng Tê Liệt trên Tacet Discord kéo dài hơn &lt;color=#fde7a1ff&gt;50%&lt;/color&gt;.
 Tacet Discord có lượng HP cao hơn.
 Địa hình trong mô phỏng được mở rộng.</t>
@@ -7349,8 +7349,8 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Mức Đe Dọa Tăng: Matrix Durability Tối Đa giảm xuống còn &lt;color=#fde7a1ff&gt;15&lt;/color&gt;. Bắt đầu với thêm &lt;color=#fde7a1ff&gt;1000&lt;/color&gt; Tín Dụng Mô Phỏng.
-Crit. Rate của Combat Machines Loại Fusion tăng &lt;color=#fde7a1ff&gt;50%&lt;/color&gt;.
+          <t>Mức Đe Dọa Tăng: Độ Bền Ma Trận Tối Đa giảm xuống còn &lt;color=#fde7a1ff&gt;15&lt;/color&gt;. Bắt đầu với thêm &lt;color=#fde7a1ff&gt;1000&lt;/color&gt; Tín Dụng Mô Phỏng.
+Crit. Rate của Máy Chiến Đấu Loại Fusion tăng &lt;color=#fde7a1ff&gt;50%&lt;/color&gt;.
 Tacet Discord có lượng HP cao hơn.
 Địa hình trong mô phỏng được mở rộng.</t>
         </is>
@@ -7421,8 +7421,8 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Mức Đe Dọa Tăng: Matrix Durability Tối Đa giảm xuống còn &lt;color=#fde7a1ff&gt;15&lt;/color&gt;. Bắt đầu với thêm &lt;color=#fde7a1ff&gt;1000&lt;/color&gt; Tín Dụng Mô Phỏng.
-Combat Machines Loại Glacio gây thêm &lt;color=#fde7a1ff&gt;30%&lt;/color&gt; sát thương.
+          <t>Mức Đe Dọa Tăng: Độ Bền Ma Trận Tối Đa giảm xuống còn &lt;color=#fde7a1ff&gt;15&lt;/color&gt;. Bắt đầu với thêm &lt;color=#fde7a1ff&gt;1000&lt;/color&gt; Tín Dụng Mô Phỏng.
+Máy Chiến Đấu Loại Glacio gây thêm &lt;color=#fde7a1ff&gt;30%&lt;/color&gt; DMG.
 Hiệu ứng Chậm và Đóng Băng trên Tacet Discord kéo dài hơn &lt;color=#fde7a1ff&gt;40%&lt;/color&gt;.
 Tacet Discord có lượng HP cao hơn.</t>
         </is>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Mức Đe Dọa Tăng: Matrix Durability Tối Đa giảm xuống còn &lt;color=#fde7a1ff&gt;15&lt;/color&gt;. Bắt đầu với thêm &lt;color=#fde7a1ff&gt;1000&lt;/color&gt; Tín Dụng Mô Phỏng.
+          <t>Mức Đe Dọa Tăng: Độ Bền Ma Trận Tối Đa giảm xuống còn &lt;color=#fde7a1ff&gt;15&lt;/color&gt;. Bắt đầu với thêm &lt;color=#fde7a1ff&gt;1000&lt;/color&gt; Tín Dụng Mô Phỏng.
 Tacet Discord có lượng HP cao hơn.
 Địa hình trong mô phỏng được mở rộng.</t>
         </is>
@@ -7560,7 +7560,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Khủng hoảng leo thang: Durability Ma Trận Tối Đa giảm xuống còn &lt;color=#fde7a1ff&gt;1&lt;/color&gt;. Bắt đầu với thêm &lt;color=#fde7a1ff&gt;1000&lt;/color&gt; Sim Creditss.
+          <t>Khủng hoảng leo thang: Độ bền Ma Trận Tối Đa giảm xuống còn &lt;color=#fde7a1ff&gt;1&lt;/color&gt;. Bắt đầu với thêm &lt;color=#fde7a1ff&gt;1000&lt;/color&gt; Sim Credits.
 Tacet Discord có lượng HP cao hơn.
 Địa hình trong mô phỏng này được mở rộng.</t>
         </is>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Khủng hoảng leo thang: Durability Ma Trận Tối Đa giảm xuống còn &lt;color=#fde7a1ff&gt;1&lt;/color&gt;. Bắt đầu với thêm &lt;color=#fde7a1ff&gt;1000&lt;/color&gt; Sim Creditss.
+          <t>Khủng hoảng leo thang: Độ bền Ma Trận Tối Đa giảm xuống còn &lt;color=#fde7a1ff&gt;1&lt;/color&gt;. Bắt đầu với thêm &lt;color=#fde7a1ff&gt;1000&lt;/color&gt; Sim Credits.
 Tacet Discord có lượng HP cao hơn.</t>
         </is>
       </c>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Mục tiêu mô phỏng</t>
+          <t>Mục Tiêu Mô Phỏng</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Physical lên Tacet Discord.</t>
+          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Vật Lý lên Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -7824,7 +7824,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Physical lên Tacet Discord.</t>
+          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Vật Lý lên Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Physical lên Tacet Discord.</t>
+          <t>Thỉnh thoảng phóng Gai Tacetite, gây Sát Thương Vật Lý lên Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Tacetite Spikes gây thêm Sát Thương và chuyển thành Electro DMG.</t>
+          <t>Gai Tổ Tacet gây thêm Sát Thương và chuyển thành Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Tacetite Spikes gây thêm Sát Thương và chuyển thành Glacio DMG.</t>
+          <t>Gai Tổ Tacet gây thêm Sát Thương và chuyển thành Sát Thương Glacio.</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Fusion DMG lên các Tacet Discord phía trước.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Sát Thương Fusion lên các Tacet Discord phía trước.</t>
         </is>
       </c>
     </row>
@@ -8149,7 +8149,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Fusion DMG lên các Tacet Discord phía trước.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Sát Thương Fusion lên các Tacet Discord phía trước.</t>
         </is>
       </c>
     </row>
@@ -8214,7 +8214,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Fusion DMG lên các Tacet Discord phía trước.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Drake, gây Sát Thương Fusion lên các Tacet Discord phía trước.</t>
         </is>
       </c>
     </row>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Hơi thở của Drake Echoes thiêu đốt mục tiêu, gây Fusion DMG theo thời gian.</t>
+          <t>Hơi thở của Drake Echoes thiêu đốt mục tiêu, gây Sát Thương Fusion theo thời gian.</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Tất cả Kháng của Tacet Discord bị ảnh hưởng bởi Glacio Beacon đều bị giảm.</t>
+          <t>Tất cả Kháng của Tacet Discord bị ảnh hưởng bởi Đèn Hiệu Glacio đều bị giảm.</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Shock gây thêm DMG.</t>
+          <t>Sốc Điện gây thêm DMG.</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Lây Nhiễm gây Sát Thương Physical.</t>
+          <t>Lây Nhiễm gây Sát Thương Vật Lý.</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Physical diện rộng.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Vật Lý diện rộng.</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Physical diện rộng.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Vật Lý diện rộng.</t>
         </is>
       </c>
     </row>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Physical diện rộng.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Junrock phát nổ khi Tacet Discord đến gần, gây Sát Thương Vật Lý diện rộng.</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Junrock Echo giờ gây Glacio DMG và làm chậm mục tiêu.</t>
+          <t>Junrock Echo giờ gây Sát Thương Glacio và làm chậm mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Electro DMG.</t>
+          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Electro DMG.</t>
+          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Electro DMG.</t>
+          <t>Thỉnh thoảng bắn ra một ngọn thương sét xuyên qua Tacet Discord với tầm vô hạn, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Thương Sét gây ít sát thương hơn, nhưng giờ thiết bị bắn ra 2 Thương Sét cùng lúc.</t>
+          <t>Thương Sét gây ít DMG hơn, nhưng giờ thiết bị bắn ra 2 Thương Sét cùng lúc.</t>
         </is>
       </c>
     </row>
@@ -9059,7 +9059,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Khi Tacet Discord đến gần, bắn mảnh Echo gây Sát Thương Physical lên mục tiêu phía trước.</t>
+          <t>Khi Tacet Discord đến gần, bắn mảnh Tổ Tacet gây Sát Thương Vật Lý lên mục tiêu phía trước.</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Khi Tacet Discord đến gần, bắn mảnh Echo gây Sát Thương Physical lên mục tiêu phía trước.</t>
+          <t>Khi Tacet Discord đến gần, bắn mảnh Tổ Tacet gây Sát Thương Vật Lý lên mục tiêu phía trước.</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Khi Tacet Discord đến gần, bắn mảnh Echo gây Sát Thương Physical lên mục tiêu phía trước.</t>
+          <t>Khi Tacet Discord đến gần, bắn mảnh Tổ Tacet gây Sát Thương Vật Lý lên mục tiêu phía trước.</t>
         </is>
       </c>
     </row>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Mảnh Echo giờ gây Fusion DMG và Thiêu Đốt mục tiêu, gây Fusion DMG theo thời gian.</t>
+          <t>Mảnh Tổ Tacet giờ gây Sát Thương Fusion và Thiêu Đốt mục tiêu, gây Sát Thương Fusion theo thời gian.</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Mỗi khi bắn mảnh Tacetite, có xác suất nhỏ gây sát thương cực cao.</t>
+          <t>Mỗi khi bắn mảnh Tacetite, có xác suất nhỏ gây DMG cực cao.</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng phun khí lạnh đông cứng, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi.</t>
+          <t>Thỉnh thoảng phun khí lạnh đông cứng, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng phun khí lạnh đông cứng, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi.</t>
+          <t>Thỉnh thoảng phun khí lạnh đông cứng, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng phun khí lạnh đông cứng, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi.</t>
+          <t>Thỉnh thoảng phun khí lạnh đông cứng, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Khí áp suất cao giờ gây Aero DMG và xóa bỏ Ô Nhiễm Tần Số trong phạm vi.</t>
+          <t>Khí áp suất cao giờ gây DMG Aero và xóa bỏ Ô Nhiễm Tần Số trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Giờ đây, xoáy nhân tạo sẽ gây Aero DMG và loại bỏ Tàng Hình của Tacet Discord.</t>
+          <t>Giờ đây, xoáy nhân tạo sẽ gây Sát Thương Aero và loại bỏ Tàng Hình của Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Physical và đẩy lùi Tacet Discord trên đường đi.</t>
+          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Vật Lý và đẩy lùi Tacet Discord trên đường đi.</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Physical và đẩy lùi Tacet Discord trên đường đi.</t>
+          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Vật Lý và đẩy lùi Tacet Discord trên đường đi.</t>
         </is>
       </c>
     </row>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Physical và đẩy lùi Tacet Discord trên đường đi.</t>
+          <t>Triệu hồi một Hoartoise Echo xoay tròn, gây Sát Thương Vật Lý và đẩy lùi Tacet Discord trên đường đi.</t>
         </is>
       </c>
     </row>
@@ -9904,7 +9904,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Hồi Âm Hoartoise gây nhiều sát thương hơn và giờ gây sát thương Hệ Fusion.</t>
+          <t>Hồi Âm Hoartoise gây nhiều DMG hơn và giờ gây DMG Hệ Fusion.</t>
         </is>
       </c>
     </row>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng giật sét một Discord trong phạm vi, gây Electro DMG.</t>
+          <t>Thỉnh thoảng giật sét một Tacet Discord trong phạm vi, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng giật sét một Discord trong phạm vi, gây Electro DMG.</t>
+          <t>Thỉnh thoảng giật sét một Tacet Discord trong phạm vi, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng giật sét một Discord trong phạm vi, gây Electro DMG.</t>
+          <t>Thỉnh thoảng giật sét một Tacet Discord trong phạm vi, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Tiêu diệt mục tiêu bằng cú sốc sẽ tạo ra bão sấm ngay tại chỗ, gây Electro DMG.</t>
+          <t>Tiêu diệt mục tiêu bằng cú sốc sẽ tạo ra bão sấm ngay tại chỗ, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Xoáy nước không còn loại bỏ Shield nữa mà khiến các Tacet Discord lơ lửng chịu nhiều Sát Thương hơn.</t>
+          <t>Xoáy nước không còn loại bỏ Khiên nữa mà khiến các Tacet Discord lơ lửng chịu nhiều Sát Thương hơn.</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10359,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Định kỳ phun ra luồng khí lạnh, gây Glacio DMG và làm chậm Tacet Discord trong phạm vi.</t>
+          <t>Định kỳ phun ra luồng khí lạnh, gây Sát Thương Glacio và làm chậm Tacet Discord trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Glacio DMG trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Sát Thương Glacio trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Glacio DMG trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Sát Thương Glacio trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Glacio DMG trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
+          <t>Định kỳ triệu hồi Ảnh Phản Chiếu Puff tấn công các Tacet Discord gần đó và gây Sát Thương Glacio trong thời gian tồn tại. Ảnh Phản Chiếu Puff có thể tự nâng cấp trong chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu Dodgem xu xuống dưới, gây Fusion DMG. Tacet Discord bị tiêu diệt bởi thiết bị có thể rơi Xu May Mắn.</t>
+          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu ném xu xuống dưới, gây Sát Thương Fusion. Tacet Discord bị tiêu diệt bởi thiết bị có thể rơi Xu May Mắn.</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu Dodgem xu xuống dưới, gây Fusion DMG. Tacet Discord bị tiêu diệt bởi thiết bị có thể rơi Xu May Mắn.</t>
+          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu ném xu xuống dưới, gây Sát Thương Fusion. Tacet Discord bị tiêu diệt bởi thiết bị có thể rơi Xu May Mắn.</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu Dodgem xu xuống dưới, gây Fusion DMG. Tacet Discord bị tiêu diệt bởi thiết bị có thể rơi Xu May Mắn.</t>
+          <t>Định kỳ triệu hồi Quái Giả Hòm Kho Báu ném xu xuống dưới, gây Sát Thương Fusion. Tacet Discord bị tiêu diệt bởi thiết bị có thể rơi Xu May Mắn.</t>
         </is>
       </c>
     </row>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Khi Discord bị Thiêu Đốt, Chest Mimic sẽ giảm Fusion RES của nó khi trúng đòn.</t>
+          <t>Khi Tacet Discord bị Thiêu Đốt, Chest Mimic sẽ giảm Kháng Fusion của nó khi trúng đòn.</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Chest Mimic gây nhiều sát thương hơn.</t>
+          <t>Rương Biến Hình gây nhiều DMG hơn.</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp) và bắn vào Tacet Discord đi qua, gây Fusion DMG cho mục tiêu trong phạm vi.</t>
+          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp) và bắn vào Tacet Discord đi qua, gây Sát Thương Fusion cho mục tiêu trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp) và bắn vào Tacet Discord đi qua, gây Fusion DMG cho mục tiêu trong phạm vi.</t>
+          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp) và bắn vào Tacet Discord đi qua, gây Sát Thương Fusion cho mục tiêu trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp) và bắn vào Tacet Discord đi qua, gây Fusion DMG cho mục tiêu trong phạm vi.</t>
+          <t>Thỉnh thoảng nạp Lõi Nổ (giới hạn nạp) và bắn vào Tacet Discord đi qua, gây Sát Thương Fusion cho mục tiêu trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Tự động bắn liên tiếp các đạn năng lượng Fusion, gây sát thương thấp</t>
+          <t>Tự động bắn liên tiếp các đạn năng lượng Fusion, gây DMG thấp</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Bắn một chùm năng lượng bất ổn nổ tung khi va chạm, gây Electro DMG cao. Có thể nạp để tăng sát thương và phạm vi nổ.</t>
+          <t>Bắn một chùm năng lượng bất ổn nổ tung khi va chạm, gây Sát Thương Electro cao. Có thể nạp để tăng DMG và phạm vi nổ.</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Tự động bắn liên tiếp các đạn năng lượng Fusion, gây sát thương thấp</t>
+          <t>Tự động bắn liên tiếp các đạn năng lượng Fusion, gây DMG thấp</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Bắn một chùm năng lượng bất ổn nổ tung khi va chạm, gây Electro DMG cao. Có thể nạp để tăng sát thương và phạm vi nổ.</t>
+          <t>Bắn một chùm năng lượng bất ổn nổ tung khi va chạm, gây Sát Thương Electro cao. Có thể nạp để tăng DMG và phạm vi nổ.</t>
         </is>
       </c>
     </row>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Tự động bắn liên tiếp các đạn năng lượng Fusion, gây sát thương thấp</t>
+          <t>Tự động bắn liên tiếp các đạn năng lượng Fusion, gây DMG thấp</t>
         </is>
       </c>
     </row>
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Bắn một chùm năng lượng bất ổn nổ tung khi va chạm, gây Electro DMG cao. Có thể nạp để tăng sát thương và phạm vi nổ.</t>
+          <t>Bắn một chùm năng lượng bất ổn nổ tung khi va chạm, gây Sát Thương Electro cao. Có thể nạp để tăng DMG và phạm vi nổ.</t>
         </is>
       </c>
     </row>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Tự động bắn liên tiếp các đạn năng lượng Fusion, gây sát thương thấp</t>
+          <t>Tự động bắn liên tiếp các đạn năng lượng Fusion, gây DMG thấp</t>
         </is>
       </c>
     </row>
@@ -12244,7 +12244,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Bắn một chùm năng lượng bất ổn nổ tung khi va chạm, gây Electro DMG cao. Có thể nạp để tăng sát thương và phạm vi nổ.</t>
+          <t>Bắn một chùm năng lượng bất ổn nổ tung khi va chạm, gây Sát Thương Electro cao. Có thể nạp để tăng DMG và phạm vi nổ.</t>
         </is>
       </c>
     </row>
@@ -12439,7 +12439,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=Ấn} vào nút để tự động bắn đạn, gây Fusion DMG. {Cus:Ipt,Touch=Touch PC=click Gamepad=Ấn} lại để dừng bắn.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút để tự động bắn đạn, gây Sát Thương Fusion. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} lại để dừng bắn.</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Bắn một chùm năng lượng bất ổn. Giữ để nạp và thả để bắn. Sau khi nạp 1 giây, gây &lt;color=#fde7a1ff&gt;300%&lt;/color&gt; Electro DMG trong phạm vi rộng hơn. Sau khi nạp 2 giây, gây &lt;color=#fde7a1ff&gt;750%&lt;/color&gt; Electro DMG trong phạm vi rộng hơn nữa.</t>
+          <t>Bắn một chùm năng lượng bất ổn. Giữ để nạp và thả để bắn. Sau khi nạp 1 giây, gây &lt;color=#fde7a1ff&gt;300%&lt;/color&gt; Sát Thương Electro trong phạm vi rộng hơn. Sau khi nạp 2 giây, gây &lt;color=#fde7a1ff&gt;750%&lt;/color&gt; Sát Thương Electro trong phạm vi rộng hơn nữa.</t>
         </is>
       </c>
     </row>
@@ -12699,7 +12699,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=Ấn} vào nút để tự động bắn đạn, gây Fusion DMG. {Cus:Ipt,Touch=Touch PC=click Gamepad=Ấn} lại để dừng bắn.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào nút để tự động bắn đạn, gây Sát Thương Fusion. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} lại để dừng bắn.</t>
         </is>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Bắn một chùm năng lượng bất ổn. Giữ để nạp và thả để bắn. Sau khi nạp 1 giây, gây &lt;color=#fde7a1ff&gt;300%&lt;/color&gt; Electro DMG trong phạm vi rộng hơn. Sau khi nạp 2 giây, gây &lt;color=#fde7a1ff&gt;750%&lt;/color&gt; Electro DMG trong phạm vi rộng hơn nữa.</t>
+          <t>Bắn một chùm năng lượng bất ổn. Giữ để nạp và thả để bắn. Sau khi nạp 1 giây, gây &lt;color=#fde7a1ff&gt;300%&lt;/color&gt; Sát Thương Electro trong phạm vi rộng hơn. Sau khi nạp 2 giây, gây &lt;color=#fde7a1ff&gt;750%&lt;/color&gt; Sát Thương Electro trong phạm vi rộng hơn nữa.</t>
         </is>
       </c>
     </row>
@@ -12959,7 +12959,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -13089,7 +13089,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Tactic Set kích nổ Combat Machines trên mặt đất để tạo ra ngọn lửa sát thương cao, với sự hỗ trợ của Combat Machines trên tường và trần.</t>
+          <t>Bộ Chiến Thuật kích nổ Máy Chiến Đấu trên mặt đất để tạo ra ngọn lửa sát thương cao, với sự hỗ trợ của Máy Chiến Đấu trên tường và trần.</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Tactic Set tạo ra Chuỗi Sét nảy giữa các mục tiêu, tăng Electro DMG và gia tăng hiệu ứng Tê Liệt.</t>
+          <t>Bộ Chiến Thuật tạo ra Chuỗi Sét nảy giữa các mục tiêu, tăng Sát Thương Electro và gia tăng hiệu ứng Tê Liệt.</t>
         </is>
       </c>
     </row>
@@ -13221,7 +13221,7 @@
       <c r="M196" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Kích hoạt Resonance Skill - Khiêu Vũ Cùng Sói hoặc Resonance Skill: Khiêu Vũ Cùng Sói - Cao Trào sẽ hồi {0} HP Tối Đa của Lupa, hút mục tiêu xung quanh và triệu hồi Bầy Sói, gây Fusion DMG mỗi giây bằng {1} Attack trong phạm vi. Sát Thương gây ra được tính là Sát Thương Basic Attack. Bầy Sói hồi {2} Resonance Energy khi trúng mục tiêu, hiệu ứng kéo dài {3} giây.</t>
+Kích hoạt Resonance Skill - Khiêu Vũ Cùng Sói hoặc Resonance Skill: Khiêu Vũ Cùng Sói - Cao Trào sẽ hồi {0} HP Tối Đa của Lupa, hút mục tiêu xung quanh và triệu hồi Bầy Sói, gây Sát Thương Fusion mỗi giây bằng {1} ATK trong phạm vi. Sát Thương gây ra được tính là Sát Thương Basic Attack. Bầy Sói hồi {2} Resonance Energy khi trúng mục tiêu, hiệu ứng kéo dài {3} giây.</t>
         </is>
       </c>
     </row>
@@ -13291,10 +13291,10 @@
       <c r="M197" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Inherent Skill - Nhớ Lấy Name Ta nhận được các tăng cường đặc biệt sau:
+Kỹ Năng Nội Tại - Nhớ Lấy Tên Ta nhận được các tăng cường đặc biệt sau:
 - Thời gian cần thiết để vào trạng thái Chạy Nước Rút giảm xuống còn {0} giây.
-- Heavy Attack - Cắn Xé Của Sói, Heavy Attack - Vuốt Sói và Đòn Mid-air Attack - Đòn Lửa gây thêm Fusion DMG bằng {1} Attack.
-- Basic Attack - Sao Rơi và Dodge Counter gây thêm Fusion DMG bằng {2} Attack và hồi phục thêm &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm} Ngọn Lửa Sói. Sử dụng Basic Attack ngay sau đó sẽ thi triển lại Basic Attack - Sao Rơi.</t>
+- Đòn ATK Mạnh - Cắn Xé Của Sói, Đòn ATK Mạnh - Vuốt Sói và Đòn ATK Giữa Không - Đòn Lửa gây thêm Sát Thương Fusion bằng {1} ATK.
+- Đòn Basic Attack - Sao Rơi và Dodge Counter Tránh gây thêm Sát Thương Fusion bằng {2} ATK và hồi phục thêm &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm} Ngọn Lửa Sói. Sử dụng Đòn Basic Attack ngay sau đó sẽ thi triển lại Đòn Basic Attack - Sao Rơi.</t>
         </is>
       </c>
     </row>
@@ -13362,8 +13362,8 @@
       <c r="M198" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Increase Attack thêm {0} và miễn nhiễm với hiệu ứng gián đoạn khi ở trạng thái Điểm Hòa Âm Cháy.
-Trong vòng {1} giây sau khi sử dụng Resonance Skill: Khiêu Vũ Cùng Sói - Cao Trào, {Cus:Ipt,Touch=Normal Attack PC=nhấn Gamepad=nhấn} để thi triển Gnash, gây Fusion DMG tổng cộng bằng {2} Attack khi trúng mục tiêu và hồi phục toàn bộ Ngọn Lửa Sói. Hiệu ứng hồi phục Ngọn Lửa Sói chỉ có thể kích hoạt tối đa một lần mỗi 8 giây.</t>
+Tăng ATK thêm {0} và miễn nhiễm với hiệu ứng gián đoạn khi ở trạng thái Điểm Hòa Âm Cháy.
+Trong vòng {1} giây sau khi sử dụng Resonance Skill: Khiêu Vũ Cùng Sói - Cao Trào, {Cus:Ipt,Touch=tap PC=press Gamepad=press} để thi triển Gnash, gây Sát Thương Fusion tổng cộng bằng {2} ATK khi trúng mục tiêu và hồi phục toàn bộ Ngọn Lửa Sói. Hiệu ứng hồi phục Ngọn Lửa Sói chỉ có thể kích hoạt tối đa một lần mỗi 8 giây.</t>
         </is>
       </c>
     </row>
@@ -13433,10 +13433,10 @@
       <c r="M199" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Glory Chói Lửa nhận được các nâng cấp sau:
-- Cooldown chiêu giảm {0}.
-- Kích hoạt kỹ năng sẽ tăng Fusion DMG thêm {1} trong {2} giây.
-- Đồng thời triệu hồi Tiếng Hú Sói hai lần tại vị trí mục tiêu, mỗi lần gây Fusion DMG bằng {3} Tấn Công và hồi {4} điểm Resonance Energy khi trúng đích.</t>
+Vinh Quang Chói Lửa nhận được các nâng cấp sau:
+- Thời gian hồi chiêu giảm {0}.
+- Kích hoạt kỹ năng sẽ tăng Sát Thương Fusion thêm {1} trong {2} giây.
+- Đồng thời triệu hồi Tiếng Hú Sói hai lần tại vị trí mục tiêu, mỗi lần gây Sát Thương Fusion bằng {3} ATK và hồi {4} điểm Resonance Energy khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -13503,7 +13503,7 @@
       <c r="M200" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Resonance Skill - Khiêu Vũ Cùng Sói và Resonance Skill: Khiêu Vũ Cùng Sói - Cao Trào làm giảm Fusion RES của mục tiêu {0} trong {1} giây khi trúng đích.</t>
+Resonance Skill - Khiêu Vũ Cùng Sói và Resonance Skill: Khiêu Vũ Cùng Sói - Cao Trào làm giảm Kháng Fusion của mục tiêu {0} trong {1} giây khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -13637,7 +13637,7 @@
       <c r="M202" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Inherent Skill - Nhớ Lấy Name Ta nhận được tăng cường đặc biệt.</t>
+Kỹ Năng Nội Tại - Nhớ Lấy Tên Ta nhận được tăng cường đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
       <c r="M203" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Increase Tấn Công và miễn nhiễm với hiệu ứng gián đoạn khi ở trạng thái Điểm Hòa Âm Cháy. Resonance Skill: Khiêu Vũ Cùng Sói - Cao Trào có thể tiếp nối bằng [Gnash], gây Sát Thương và hồi phục Ngọn Lửa Sói.</t>
+Tăng ATK và miễn nhiễm với hiệu ứng gián đoạn khi ở trạng thái Điểm Hòa Âm Cháy. Resonance Skill: Khiêu Vũ Cùng Sói - Cao Trào có thể tiếp nối bằng [Gnash], gây Sát Thương và hồi phục Ngọn Lửa Sói.</t>
         </is>
       </c>
     </row>
@@ -13771,7 +13771,7 @@
       <c r="M204" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Giảm Cooldown chiêu của Glory Chói Lửa và tăng Sát Thương của kỹ năng này.</t>
+Giảm thời gian hồi chiêu của Vinh Quang Chói Lửa và tăng Sát Thương của kỹ năng này.</t>
         </is>
       </c>
     </row>
@@ -13838,7 +13838,7 @@
       <c r="M205" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Resonance Skill - Khiêu Vũ Cùng Sói và Khiêu Vũ Cùng Sói - Cao Trào sẽ làm giảm Fusion RES của mục tiêu khi trúng đích.</t>
+Resonance Skill - Khiêu Vũ Cùng Sói và Khiêu Vũ Cùng Sói - Cao Trào sẽ làm giảm Kháng Fusion của mục tiêu khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -13907,9 +13907,9 @@
       <c r="M206" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Mục tiêu trúng Resonance Skill - Cartethyia sẽ chịu thêm Aero DMG bằng {0} HP tối đa và dính thêm &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S= tầng P= tầng} Erosion Aero. Khi sử dụng Resonance Skill - Cartethyia, triệu hồi thêm một Kiếm Shadow Thần Thánh và giảm Cooldown chiêu của Resonance Liberation đi {2} giây.
-- Khả năng chống gián đoạn tăng lên khi sử dụng Resonance Skill - Kiếm Đáp Lời Sóng và Resonance Skill - Tempest Phá Tan Triều Cường. Sát Thương của chúng được Khuếch Đại thêm {3}. Trúng mục tiêu bằng cả hai kỹ năng sẽ gây thêm &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S= tầng P= tầng} Erosion Aero.
-- Ngoài ra, Cartethyia và Fleurdelys nhận được Lãnh Địa Gió: Khi trúng mục tiêu, tăng tối đa 3 tầng Erosion Aero mà mục tiêu có thể nhận trong 10 giây. Hiệu ứng này không cộng dồn.</t>
+- Mục tiêu trúng Resonance Skill - Cartethyia sẽ chịu thêm Sát Thương Aero bằng {0} HP tối đa và dính thêm &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S= tầng P= tầng} Xói Mòn Aero. Khi sử dụng Resonance Skill - Cartethyia, triệu hồi thêm một Kiếm Bóng Tối Thần Thánh và giảm thời gian hồi chiêu của Resonance Liberation đi {2} giây.
+- Khả năng chống gián đoạn tăng lên khi sử dụng Resonance Skill - Kiếm Đáp Lời Sóng và Resonance Skill - Bão Tố Phá Tan Triều Cường. Sát Thương của chúng được Khuếch Đại thêm {3}. Trúng mục tiêu bằng cả hai kỹ năng sẽ gây thêm &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S= tầng P= tầng} Xói Mòn Aero.
+- Ngoài ra, Cartethyia và Fleurdelys nhận được Lãnh Địa Gió: Khi trúng mục tiêu, tăng tối đa 3 tầng Xói Mòn Aero mà mục tiêu có thể nhận trong 10 giây. Hiệu ứng này không cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -13977,10 +13977,10 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Mid-air Attack]&lt;/color&gt;
-- Khi Cartethyia sở hữu Heart of Virtue, Mandate of Divinity hoặc Power of Discord, Đòn Lao Xuống của Đòn Mid-air Attack - Cartethyia sẽ triệu hồi Kiếm Bóng tương ứng khi trúng mục tiêu. Mỗi Kiếm Bóng gây Aero DMG bằng {0} HP tối đa, được tính là Aero DMG Erosion. Cooldown chiêu của Resonance Skill – Cartethyia giảm 3 giây.
-- Nếu cả 3 Kiếm Bóng được triệu hồi trong một lần Đòn Mid-air Attack - Cartethyia, sẽ bước vào trạng thái Blessed Storm.
-Blessed Storm: Trong trạng thái Blessed Storm, hồi phục toàn bộ thể lực. Increase sát thương của Kiếm Bóng do Đòn Mid-air Attack - Cartethyia tiếp theo triệu hồi lên {1} HP tối đa, sau đó kết thúc ngay trạng thái Blessed Storm và loại bỏ Heart of Virtue, Mandate of Divinity cùng Power of Discord. Sử dụng Resonance Liberation - Blade of Howling Squall cũng sẽ kết thúc Blessed Storm.</t>
+          <t>&lt;color=#c49e55&gt;[Đòn Tấn Công Giữa Không]&lt;/color&gt;
+- Khi Cartethyia sở hữu Heart of Virtue, Mandate of Divinity hoặc Power of Discord, Đòn Lao Xuống của Đòn Tấn Công Giữa Không - Cartethyia sẽ triệu hồi Kiếm Bóng tương ứng khi trúng mục tiêu. Mỗi Kiếm Bóng gây DMG Aero bằng {0} HP tối đa, được tính là DMG Aero Erosion. Thời gian hồi chiêu của Resonance Skill – Cartethyia giảm 3 giây.
+- Nếu cả 3 Kiếm Bóng được triệu hồi trong một lần Đòn Tấn Công Giữa Không - Cartethyia, sẽ bước vào trạng thái Blessed Storm.
+Blessed Storm: Trong trạng thái Blessed Storm, hồi phục toàn bộ thể lực. Tăng DMG của Kiếm Bóng do Đòn Tấn Công Giữa Không - Cartethyia tiếp theo triệu hồi lên {1} HP tối đa, sau đó kết thúc ngay trạng thái Blessed Storm và loại bỏ Heart of Virtue, Mandate of Divinity cùng Power of Discord. Sử dụng Resonance Liberation - Blade of Howling Squall cũng sẽ kết thúc Blessed Storm.</t>
         </is>
       </c>
     </row>
@@ -14055,15 +14055,15 @@
       <c r="M208" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- Kích hoạt Resonance Liberation - Lời Nguyện Cầu Chân Thành của Kỵ Sĩ sẽ ban 2 tầng Thánh Khiết. Nếu Fleurdelys có 120 điểm Conviction và Thánh Khiết, Resonance Skill sẽ được thay thế bằng Resonance Skill - Thẩm Phán Tội Ác.
+- Kích hoạt Resonance Liberation - Lời Nguyện Cầu Chân Thành của Kỵ Sĩ sẽ ban 2 tầng Thánh Khiết. Nếu Fleurdelys có 120 điểm Niềm Tin và Thánh Khiết, Resonance Skill sẽ được thay thế bằng Resonance Skill - Thẩm Phán Tội Ác.
 - Resonance Skill - Thẩm Phán Tội Ác:
-Kích hoạt kỹ năng sẽ tiêu hao 1 tầng Thánh Khiết và toàn bộ Conviction, gây Aero DMG bằng {0} HP tối đa lên tất cả mục tiêu trong một khu vực theo đường thẳng phía trước. Sát thương gây ra được tính là cả Sát Thương Erosion Aero và Sát Thương Basic Attack. Sau đó, áp đặt &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng Erosion Aero} lên mục tiêu trúng đòn.
-Sau khi kích hoạt Resonance Skill - Thẩm Phán Tội Ác, Fleurdelys sẽ tái nhập Hiện Thể và nhận 1 tầng Nghi Thức Freedom, có thể tích lũy tối đa 2 tầng. Kích hoạt Resonance Liberation - Lưỡi Kiếm Gió Gào của Fleurdelys hoặc Đòn Mid-air Attack - Cartethyia của Cartethyia trong trạng thái Bão Phước Lành sẽ tiêu hao toàn bộ tầng Nghi Thức Freedom, mỗi tầng tiêu hao làm tăng Hệ Số Sát Thương của đòn tấn công này thêm {2}. Sau đó, xóa toàn bộ Thánh Khiết.
+Kích hoạt kỹ năng sẽ tiêu hao 1 tầng Thánh Khiết và toàn bộ Niềm Tin, gây Sát Thương Aero bằng {0} HP tối đa lên tất cả mục tiêu trong một khu vực theo đường thẳng phía trước. DMG gây ra được tính là cả Sát Thương Xói Mòn Aero và Sát Thương Đòn Basic Attack. Sau đó, áp đặt &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng Xói Mòn Aero} lên mục tiêu trúng đòn.
+Sau khi kích hoạt Resonance Skill - Thẩm Phán Tội Ác, Fleurdelys sẽ tái nhập Hiện Thể và nhận 1 tầng Nghi Thức Tự Do, có thể tích lũy tối đa 2 tầng. Kích hoạt Resonance Liberation - Lưỡi Kiếm Gió Gào của Fleurdelys hoặc Đòn Tấn Công Giữa Không - Cartethyia của Cartethyia trong trạng thái Bão Phước Lành sẽ tiêu hao toàn bộ tầng Nghi Thức Tự Do, mỗi tầng tiêu hao làm tăng Hệ Số Sát Thương của đòn tấn công này thêm {2}. Sau đó, xóa toàn bộ Thánh Khiết.
 - Khi Fleurdelys lần đầu biến hình trở lại thành Cartethyia trong Hiện Thể, cô sẽ kích hoạt Kỹ Năng Giới Thiệu - Kiếm Khắc Dấu Vết Thủy Triều và tiêu hao 1 tầng Thánh Khiết để nhận Lời Thề Bất Diệt trong {3} giây.
 Lời Thề Bất Diệt:
-- Tất cả sát thương do Cartethyia gây ra được Khuếch Đại thêm {4}.
-- Khoảng thời gian kích hoạt Sát Thương Erosion Aero lên mục tiêu trong phạm vi nhất định quanh Cartethyia giảm 50%, và Sát Thương Erosion Aero được Khuếch Đại thêm 50%.
-- Nếu Cartethyia đồng thời sở hữu Heart of Virtue, Mandate of Divinity và Quyền Năng Bất Hòa mà không ở trạng thái Bão Phước Lành, Đòn Mid-air Attack - Cartethyia khi trúng mục tiêu sẽ gia hạn Lời Thề Bất Diệt thêm {5} giây và ban 1 tầng Nghi Thức Freedom.</t>
+- Tất cả DMG do Cartethyia gây ra được Khuếch Đại thêm {4}.
+- Khoảng thời gian kích hoạt Sát Thương Xói Mòn Aero lên mục tiêu trong phạm vi nhất định quanh Cartethyia giảm 50%, và Sát Thương Xói Mòn Aero được Khuếch Đại thêm 50%.
+- Nếu Cartethyia đồng thời sở hữu Trái Tim Nhân Đức, Thiên Mệnh và Quyền Năng Bất Hòa mà không ở trạng thái Bão Phước Lành, Đòn Tấn Công Giữa Không - Cartethyia khi trúng mục tiêu sẽ gia hạn Lời Thề Bất Diệt thêm {5} giây và ban 1 tầng Nghi Thức Tự Do.</t>
         </is>
       </c>
     </row>
@@ -14131,8 +14131,8 @@
       <c r="M209" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Basic Attack - Fleurdelys Stage 4, Mid-air Attack - Fleurdelys Stage 2, Dodge Counter - Fleurdelys, Resonance Skill - May Tempest Break the Tides và Intro Skill - Kiếm to Mark Tide's Trace sẽ triệu hồi một đợt Mưa Thanh Tẩy. Nếu Cartethyia sở hữu Heart of Virtue, Mandate of Divinity và Power of Discord, Mid-air Attack - Cartethyia cũng sẽ triệu hồi một đợt Mưa Thanh Tẩy.
-Mưa Thanh Tẩy giảm Cooldown chiêu của Resonance Skill - Kiếm to Answer Waves' Call đi {0}s và gây Aero DMG bằng {1} tổng HP tối đa lên các mục tiêu trong phạm vi. Sát Thương gây ra được tính là cả Sát Thương Erosion Aero và Sát Thương Basic Attack.</t>
+Basic Attack - Fleurdelys Giai Đoạn 4, Tấn Công Giữa Không - Fleurdelys Giai Đoạn 2, Dodge Counter Tránh - Fleurdelys, Resonance Skill - May Tempest Break the Tides và Kỹ Năng Khởi Động - Kiếm đơn to Mark Tide's Trace sẽ triệu hồi một đợt Mưa Thanh Tẩy. Nếu Cartethyia sở hữu Heart of Virtue, Mandate of Divinity và Power of Discord, Tấn Công Giữa Không - Cartethyia cũng sẽ triệu hồi một đợt Mưa Thanh Tẩy.
+Mưa Thanh Tẩy giảm thời gian hồi chiêu của Resonance Skill - Kiếm đơn to Answer Waves' Call đi {0}s và gây Sát Thương Aero bằng {1} tổng HP tối đa lên các mục tiêu trong phạm vi. Sát Thương gây ra được tính là cả Sát Thương Xói Mòn Aero và Sát Thương Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -14200,8 +14200,8 @@
       <c r="M210" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Sử dụng Resonance Liberation - Blade of Howling Squall và Resonance Skill - Adjudicator of Evil sẽ nhận được Blade of Defiance. Nếu Cartethyia sở hữu Heart of Virtue, Mandate of Divinity và Power of Discord, sử dụng Mid-air Attack - Cartethyia cũng sẽ nhận được Blade of Defiance.
-Blade of Defiance tăng HP tối đa của cô lên {0} và khiến toàn bộ sát thương gây ra bỏ qua {1} Aero RES của mục tiêu, hiệu ứng kéo dài {2}s và có thể chồng chất tối đa {3} lần.</t>
+Sử dụng Resonance Liberation - Blade of Howling Squall và Resonance Skill - Adjudicator of Evil sẽ nhận được Blade of Defiance. Nếu Cartethyia sở hữu Heart of Virtue, Mandate of Divinity và Power of Discord, sử dụng Tấn Công Giữa Không - Cartethyia cũng sẽ nhận được Blade of Defiance.
+Blade of Defiance tăng HP tối đa của cô lên {0} và khiến toàn bộ sát thương gây ra bỏ qua {1} Kháng Aero của mục tiêu, hiệu ứng kéo dài {2}s và có thể chồng chất tối đa {3} lần.</t>
         </is>
       </c>
     </row>
@@ -14269,7 +14269,7 @@
       <c r="M211" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Resonance Skill - Cartethyia, Resonance Skill - Kiếm Đáp Lời Sóng, và Resonance Skill - Tempest Phá Tan Triều Khúc gây thêm sát thương và gây Erosion Aero lên mục tiêu trúng đòn.
+Resonance Skill - Cartethyia, Resonance Skill - Kiếm Đáp Lời Sóng, và Resonance Skill - Bão Tố Phá Tan Triều Khúc gây thêm DMG và gây Xói Mòn Aero lên mục tiêu trúng đòn.
 Cartethyia và Fleurdelys nhận được Lãnh Địa Gió.</t>
         </is>
       </c>
@@ -14336,8 +14336,8 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Mid-air Attack]&lt;/color&gt;
-Đòn Mid-air Attack - Cartethyia được tăng cường đặc biệt và triệu hồi Kiếm Bóng gây sát thương bổ sung.</t>
+          <t>&lt;color=#c49e55&gt;[Đòn Tấn Công Giữa Không]&lt;/color&gt;
+Đòn Tấn Công Giữa Không - Cartethyia được tăng cường đặc biệt và triệu hồi Kiếm Bóng gây DMG bổ sung.</t>
         </is>
       </c>
     </row>
@@ -14407,8 +14407,8 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
 Fleurdelys nhận được Resonance Skill - Kẻ Phán Xét Ác Nghiệp trong một số tình huống nhất định.
-Resonance Liberation - Lưỡi Kiếm Của Bão Gào và Đòn Mid-air Attack - Cartethyia được tăng cường đặc biệt.
-Increase Sát Thương gây ra bởi Cartethyia.</t>
+Resonance Liberation - Lưỡi Kiếm Của Bão Gào và Đòn Tấn Công Giữa Không - Cartethyia được tăng cường đặc biệt.
+Tăng Sát Thương gây ra bởi Cartethyia.</t>
         </is>
       </c>
     </row>
@@ -14477,7 +14477,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
 Kích hoạt một số kỹ năng của Fleurdelys và Cartethyia sẽ triệu hồi Mưa Thanh Tẩy.
-Mưa Thanh Tẩy gây Sát Thương và giảm Cooldown chiêu của Resonance Skill - Kiếm Đáp Lời Sóng.</t>
+Mưa Thanh Tẩy gây Sát Thương và giảm thời gian hồi chiêu của Resonance Skill - Kiếm Đáp Lời Sóng.</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       <c r="M215" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Kích hoạt Resonance Liberation - Lưỡi Kiếm Gào Thét, Resonance Skill - Kẻ Trừng Ác và Mid-air Attack - Cartethyia sẽ tăng HP Tối Đa và khiến toàn bộ Sát Thương gây ra bỏ qua Aero RES của mục tiêu.</t>
+Kích hoạt Resonance Liberation - Lưỡi Kiếm Gào Thét, Resonance Skill - Kẻ Trừng Ác và Tấn Công Giữa Không - Cartethyia sẽ tăng HP Tối Đa và khiến toàn bộ Sát Thương gây ra bỏ qua Kháng Aero của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -14609,7 +14609,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Increase sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; từ Echoes tạo ra qua &lt;te href=851008&gt;&lt;color=#c79f49&gt;Integration&lt;/color&gt;&lt;/te&gt; lên {0}.</t>
+          <t>Tăng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; từ Echo tạo ra qua &lt;te href=851008&gt;&lt;color=#c79f49&gt;Tích Hợp&lt;/color&gt;&lt;/te&gt; lên {0}.</t>
         </is>
       </c>
     </row>
@@ -14740,8 +14740,8 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Attack cơ bản triệu hồi một quả cầu lửa khi trúng mục tiêu, gây Fusion DMG bằng 150% Attack, được tính là Sát Thương Basic Attack. Hiệu ứng này kích hoạt mỗi 3 giây một lần.
-Khi ở trạng thái [Divined Dream], quả cầu lửa được tăng cường và gây Sát Thương bằng 300% Attack.</t>
+          <t>ATK cơ bản triệu hồi một quả cầu lửa khi trúng mục tiêu, gây Sát Thương Fusion bằng 150% ATK, được tính là Sát Thương Basic Attack. Hiệu ứng này kích hoạt mỗi 3 giây một lần.
+Khi ở trạng thái [Divined Dream], quả cầu lửa được tăng cường và gây Sát Thương bằng 300% ATK.</t>
         </is>
       </c>
     </row>
@@ -14807,8 +14807,8 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Skill Echo tạo ra một cơn bão tại khu vực mục tiêu, gây Sát Thương Hàng Không bằng 50% Tấn Công cho mục tiêu trong phạm vi 4 lần, được tính là Sát Thương Kỹ Năng Echo.
-Khi ở trạng thái [Giấc Mơ Tiên Tri], cơn bão được tăng cường và gây Sát Thương bằng 100% Tấn Công.</t>
+          <t>Kỹ năng Tiếng Vọng tạo ra một cơn bão tại khu vực mục tiêu, gây Sát Thương Hàng Không bằng 50% ATK cho mục tiêu trong phạm vi 4 lần, được tính là Sát Thương Kỹ Năng Tiếng Vọng.
+Khi ở trạng thái [Giấc Mơ Tiên Tri], cơn bão được tăng cường và gây Sát Thương bằng 100% ATK.</t>
         </is>
       </c>
     </row>
@@ -14874,8 +14874,8 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation triệu hồi 5 tia sét đánh vào các mục tiêu gần đó, mỗi tia gây Electro DMG bằng 300% Tấn Công, được tính là Sát Thương Resonance Liberation. Hiệu ứng này kích hoạt mỗi 8 giây một lần.
-Khi ở trạng thái [Divined Dream], các tia sét được tăng cường và gây Sát Thương bằng 600% Tấn Công. Khi bước vào trạng thái [Divined Dream], tất cả Resonators trong đội sẽ được phục hồi 50% Resonance Energy.</t>
+          <t>Kích hoạt Resonance Liberation triệu hồi 5 tia sét đánh vào các mục tiêu gần đó, mỗi tia gây Sát Thương Electro bằng 300% ATK, được tính là Sát Thương Resonance Liberation. Hiệu ứng này kích hoạt mỗi 8 giây một lần.
+Khi ở trạng thái [Divined Dream], các tia sét được tăng cường và gây Sát Thương bằng 600% ATK. Khi bước vào trạng thái [Divined Dream], tất cả Resonator trong đội sẽ được phục hồi 50% Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -14941,8 +14941,8 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Giới Thiệu triệu hồi Vụ Nổ Băng tấn công mục tiêu, gây Glacio DMG bằng 400% Tấn Công, được tính là Sát Thương Resonance Skill.
-Khi ở trạng thái [Giấc Mơ Tiên Tri], Vụ Nổ Băng được tăng cường và gây Sát Thương bằng 800% Tấn Công. Khi bước vào [Giấc Mơ Tiên Tri], tất cả Resonators trong đội sẽ hồi phục 50% Concerto Energy.</t>
+          <t>Kích hoạt Kỹ Năng Giới Thiệu triệu hồi Vụ Nổ Băng tấn công mục tiêu, gây Sát Thương Glacio bằng 400% ATK, được tính là Sát Thương Resonance Skill.
+Khi ở trạng thái [Giấc Mơ Tiên Tri], Vụ Nổ Băng được tăng cường và gây Sát Thương bằng 800% ATK. Khi bước vào [Giấc Mơ Tiên Tri], tất cả Resonator trong đội sẽ hồi phục 50% Concerto Energy.</t>
         </is>
       </c>
     </row>
@@ -15008,8 +15008,8 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], Resonators chủ động mất 3% HP tối đa và gây sát thương bằng 15% HP tối đa cho mục tiêu xung quanh, được tính là sát thương Basic Attack. Khi HP của Resonators dưới 1, đòn tấn công này không tiêu hao HP.
-Sử dụng Resonance Skill hoặc Resonance Liberation sẽ hồi phục 10% HP tối đa cho tất cả Resonators trong đội.</t>
+          <t>Khi ở trong [Giấc Mộng Tiên Tri], Resonator chủ động mất 3% HP tối đa và gây DMG bằng 15% HP tối đa cho mục tiêu xung quanh, được tính là DMG Basic Attack. Khi HP của Resonator dưới 1, đòn tấn công này không tiêu hao HP.
+Sử dụng Resonance Skill hoặc Resonance Liberation sẽ hồi phục 10% HP tối đa cho tất cả Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -15074,7 +15074,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], gây sát thương sẽ giúp tất cả Resonators trong đội nhận được một tầng [Revealed Heart], tăng Crit. Rate thêm 1.6% và Crit. DMG thêm 2.4%, có thể chồng chất tối đa 100 lần. Tất cả các tầng sẽ bị loại bỏ khi kết thúc [Divined Dream].</t>
+          <t>Khi ở trong [Divined Dream], gây DMG sẽ giúp tất cả Resonator trong đội nhận được một tầng [Revealed Heart], tăng Crit. Rate thêm 1.6% và Crit. DMG thêm 2.4%, có thể chồng chất tối đa 100 lần. Tất cả các tầng sẽ bị loại bỏ khi kết thúc [Divined Dream].</t>
         </is>
       </c>
     </row>
@@ -15141,9 +15141,9 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], thời gian xung quanh Resonator chủ động trôi chậm đi 90%. Mỗi lần gây sát thương sẽ cộng thêm một tầng [Temporal Power], tối đa 100 tầng.
-Tất cả các tầng sẽ bị loại bỏ khi kết thúc [Divined Dream]. Mỗi 10 tầng bị loại bỏ sẽ gây Spectro DMG bằng 900% Tấn Công cho mục tiêu trong khu vực thời gian bị chậm lại, được tính là sát thương Resonance Liberation. Nếu số tầng bị loại bỏ ít hơn 10, gây Spectro DMG bằng 125% Tấn Công.
-Thời gian của [Divined Dream] giảm xuống còn 3 giây.</t>
+          <t>Khi ở trong [Giấc Mộng Tiên Tri], thời gian xung quanh Resonator chủ động trôi chậm đi 90%. Mỗi lần gây DMG sẽ cộng thêm một tầng [Temporal Power], tối đa 100 tầng.
+Tất cả các tầng sẽ bị loại bỏ khi kết thúc [Giấc Mộng Tiên Tri]. Mỗi 10 tầng bị loại bỏ sẽ gây DMG Spectro bằng 900% ATK cho mục tiêu trong khu vực thời gian bị chậm lại, được tính là DMG Resonance Liberation. Nếu số tầng bị loại bỏ ít hơn 10, gây DMG Spectro bằng 125% ATK.
+Thời gian của [Giấc Mộng Tiên Tri] giảm xuống còn 3 giây.</t>
         </is>
       </c>
     </row>
@@ -15208,7 +15208,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], mỗi 20 tầng Erosion Aero hoặc Spectro Frazzle gây ra sẽ kích hoạt một loạt kiếm tấn công mục tiêu 5 lần. Mỗi đòn gây Aero DMG bằng 240% Tấn Công và áp dụng thêm 1 tầng Erosion Aero và Spectro Frazzle.</t>
+          <t>Khi ở trong [Divined Dream], mỗi 20 tầng Xói Mòn Aero hoặc Rối Loạn Spectro gây ra sẽ kích hoạt một loạt kiếm tấn công mục tiêu 5 lần. Mỗi đòn gây Sát Thương Aero bằng 240% ATK và áp dụng thêm 1 tầng Xói Mòn Aero và Rối Loạn Spectro.</t>
         </is>
       </c>
     </row>
@@ -15274,8 +15274,8 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators kích hoạt đang hoạt động nhận Shield, tất cả Resonators trong đội sẽ nhận một lớp [Glory], có thể chồng chất tối đa 100 lần.
-Khi ở trạng thái [Giấc Mơ Thần Thánh], gây Sát Thương Heavy Attack sẽ tiêu hao 1 lớp [Glory] để khuếch đại sát thương lần đó lên 50%. Khi bước vào [Giấc Mơ Thần Thánh], tất cả Resonators trong đội sẽ nhận 10 lớp [Glory] và một lớp Shield tương đương 50% HP tối đa, kéo dài trong 10 phút.</t>
+          <t>Mỗi khi Resonator kích hoạt đang hoạt động nhận Khiên, tất cả Resonator trong đội sẽ nhận một lớp [Vinh Quang], có thể chồng chất tối đa 100 lần.
+Khi ở trạng thái [Giấc Mơ Thần Thánh], gây Sát Thương Đòn Nặng sẽ tiêu hao 1 lớp [Vinh Quang] để khuếch đại DMG lần đó lên 50%. Khi bước vào [Giấc Mơ Thần Thánh], tất cả Resonator trong đội sẽ nhận 10 lớp [Vinh Quang] và một lớp Khiên tương đương 50% HP tối đa, kéo dài trong 10 phút.</t>
         </is>
       </c>
     </row>
@@ -15340,7 +15340,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Sau khi [Blaze Sigil] kích hoạt, một quả cầu lửa bổ sung sẽ tự động xuất hiện sau 1,5 giây. Sau khi [Blaze Sigil] gây sát thương, Basic Attack của tất cả Resonators sẽ tăng thêm 75% trong 2 giây.</t>
+          <t>Sau khi [Blaze Sigil] kích hoạt, một quả cầu lửa bổ sung sẽ tự động xuất hiện sau 1,5 giây. Sau khi [Blaze Sigil] gây DMG, Basic Attack của tất cả Resonator sẽ tăng thêm 75% trong 2 giây.</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Basic Attack sẽ kích hoạt ngay [Blaze Sigil]. Khi [Blaze Sigil] gây sát thương, có 25% cơ hội kích hoạt thêm một lần [Blaze Sigil], có thể kích hoạt lại sau mỗi 0.3 giây.</t>
+          <t>Gây Sát Thương Basic Attack sẽ kích hoạt ngay [Blaze Sigil]. Khi [Blaze Sigil] gây DMG, có 25% cơ hội kích hoạt thêm một lần [Blaze Sigil], có thể kích hoạt lại sau mỗi 0.3 giây.</t>
         </is>
       </c>
     </row>
@@ -15536,8 +15536,8 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Skill Echo của tất cả Resonators trong đội gây thêm 75% Sát Thương và giảm 30% Thời Gian Cooldown.
-Khi ở trạng thái [Divined Dream], gây Sát Thương bằng Skill Echo sẽ giảm 3% Thời Gian Cooldown của Skill Echo cho tất cả Resonators trong đội, kích hoạt mỗi giây một lần.</t>
+          <t>Kỹ năng Echo của tất cả Resonator trong đội gây thêm 75% Sát Thương và giảm 30% Thời gian hồi Chiêu.
+Khi ở trạng thái [Divined Dream], gây Sát Thương bằng Kỹ năng Echo sẽ giảm 3% Thời gian hồi Chiêu của Kỹ năng Echo cho tất cả Resonator trong đội, kích hoạt mỗi giây một lần.</t>
         </is>
       </c>
     </row>
@@ -15602,7 +15602,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], gây Sát Thương Kỹ Năng Echo sẽ tăng tổng Sát Thương của tất cả Resonators trong đội lên 2% trong 5 giây, có thể chồng chất tối đa 50 lần.</t>
+          <t>Khi ở trong [Divined Dream], gây Sát Thương Kỹ Năng Echo sẽ tăng tổng Sát Thương của tất cả Resonator trong đội lên 2% trong 5 giây, có thể chồng chất tối đa 50 lần.</t>
         </is>
       </c>
     </row>
@@ -15667,7 +15667,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Kích hoạt [Huy Hiệu Bão Tố] sẽ tăng 5% Sát Thương của tất cả Resonators trong đội và tăng thêm 5% Sát Thương Kỹ Năng Echo trong 10 giây. Hiệu ứng này có thể chồng chất lên đến 6 lần.</t>
+          <t>Kích hoạt [Huy Hiệu Bão Tố] sẽ tăng 5% Sát Thương của tất cả Resonator trong đội và tăng thêm 5% Sát Thương Kỹ Năng Echo trong 10 giây. Hiệu ứng này có thể chồng chất lên đến 6 lần.</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       <c r="M233" t="inlineStr">
         <is>
           <t>Tổng Sát Thương gây ra bởi [Hurricane Sigil] tăng thêm 50%.
-Trong trạng thái [Divined Dream], khi [Hurricane Sigil] gây sát thương, nó sẽ gây thêm một lần Aero DMG bằng 200% Tấn Công. Đòn tấn công này kích hoạt [Hurricane Sigil] thêm một lần nữa, được tính là Sát Thương Kỹ Năng Echo và có thể kích hoạt mỗi 2 giây một lần.</t>
+Trong trạng thái [Divined Dream], khi [Hurricane Sigil] gây DMG, nó sẽ gây thêm một lần Aero DMG bằng 200% ATK. Đòn tấn công này kích hoạt [Hurricane Sigil] thêm một lần nữa, được tính là Sát Thương Kỹ Năng Echo và có thể kích hoạt mỗi 2 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -15865,8 +15865,8 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], sử dụng Resonance Liberation sẽ tăng Crit. DMG của tất cả Resonators trong đội lên 20% trong 10 giây, có thể chồng chất tối đa 5 lần.
-Khi bước vào [Divined Dream], tất cả Resonators trong đội sẽ được hồi đầy Resonance Energy và loại bỏ Cooldown chiêu của Resonance Liberation.</t>
+          <t>Khi ở trong [Divined Dream], sử dụng Resonance Liberation sẽ tăng Crit. DMG của tất cả Resonator trong đội lên 20% trong 10 giây, có thể chồng chất tối đa 5 lần.
+Khi bước vào [Divined Dream], tất cả Resonator trong đội sẽ được hồi đầy Resonance Energy và loại bỏ Thời gian hồi chiêu của Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -15931,7 +15931,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Tổng Sát Thương gây ra bởi [Thunder Sigil] tăng thêm 50%. Khi [Thunder Sigil] gây sát thương, nó giảm 3% Cooldown chiêu của Kỹ Năng Resonance Liberation cho tất cả Resonators trong đội và hồi phục 10 điểm Resonance Energy.</t>
+          <t>Tổng Sát Thương gây ra bởi [Thunder Sigil] tăng thêm 50%. Khi [Thunder Sigil] gây DMG, nó giảm 3% Thời gian hồi chiêu của Kỹ Năng Giải Cứu Cộng Hưởng cho tất cả Resonator trong đội và hồi phục 10 điểm Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -16130,7 +16130,7 @@
       <c r="M239" t="inlineStr">
         <is>
           <t>Mục tiêu trúng [Ấn Ký Băng Giá] sẽ nhận một tầng [Hạ Thân Nhiệt] trong 6 giây, tối đa 3 tầng. Khi đạt tối đa, tất cả tầng [Hạ Thân Nhiệt] sẽ bị xóa và mục tiêu bị [Đóng Băng] trong 4 giây.
-Mục tiêu bị [Đóng Băng] sẽ chịu thêm 50% sát thương từ mọi nguồn và gây ít hơn 50% sát thương.</t>
+Mục tiêu bị [Đóng Băng] sẽ chịu thêm 50% DMG từ mọi nguồn và gây ít hơn 50% DMG.</t>
         </is>
       </c>
     </row>
@@ -16195,7 +16195,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Khi [Blizzard Sigil] được kích hoạt, tất cả Resonators trong đội nhận thêm 20% Sát thương Skill Cộng hưởng trong 15 giây, tối đa 5 tầng.</t>
+          <t>Khi [Blizzard Sigil] được kích hoạt, tất cả Resonator trong đội nhận thêm 20% DMG Kỹ năng Cộng hưởng trong 15 giây, tối đa 5 tầng.</t>
         </is>
       </c>
     </row>
@@ -16260,7 +16260,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Tổng Sát Thương gây ra bởi [Blizzard Sigil] tăng thêm 30%, và phạm vi tác động được mở rộng thêm 30%. Khi trúng mục tiêu, [Blizzard Sigil] hồi phục 10% Concerto Energy cho tất cả Resonators trong đội.</t>
+          <t>Tổng Sát Thương gây ra bởi [Blizzard Sigil] tăng thêm 30%, và phạm vi tác động được mở rộng thêm 30%. Khi trúng mục tiêu, [Blizzard Sigil] hồi phục 10% Concerto Energy cho tất cả Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -16326,7 +16326,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Resonator đang kích hoạt mất 5% HP tối đa mỗi giây và gây sát thương bằng 30% HP tối đa.
+          <t>Resonator đang kích hoạt mất 5% HP tối đa mỗi giây và gây DMG bằng 30% HP tối đa.
 Khi nhận đòn chí mạng, họ hồi phục 10% HP tối đa và trở nên miễn nhiễm với cái chết trong 5 giây. Hiệu ứng này chỉ kích hoạt một lần mỗi 3 phút.</t>
         </is>
       </c>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Mỗi lần mục tiêu chịu sát thương từ [Spree Sigil], chúng sẽ nhận 1 tầng [Berserk], tăng tổng Sát Thương nhận vào từ mọi nguồn thêm 15% trong 15 giây, tối đa 5 tầng.</t>
+          <t>Mỗi lần mục tiêu chịu DMG từ [Spree Sigil], chúng sẽ nhận 1 tầng [Berserk], tăng tổng Sát Thương nhận vào từ mọi nguồn thêm 15% trong 15 giây, tối đa 5 tầng.</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Khi một Resonators gây sát thương trong [Divined Dream], toàn bộ Resonators trong đội sẽ được tăng HP tối đa thêm 0,8% trong 30 giây, có thể tích lũy tối đa 150 lần.</t>
+          <t>Khi một Resonator gây sát thương trong [Divined Dream], toàn bộ Resonator trong đội sẽ được tăng HP tối đa thêm 0,8% trong 30 giây, có thể tích lũy tối đa 150 lần.</t>
         </is>
       </c>
     </row>
@@ -16522,7 +16522,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], mỗi 1 HP mất đi, Resonator đang hoạt động sẽ nhận được 0.003% Tăng Sát Thương cho tất cả các loại sát thương.</t>
+          <t>Khi ở trong [Divined Dream], mỗi 1 HP mất đi, Resonator đang hoạt động sẽ nhận được 0.003% Tăng Sát Thương cho tất cả các loại DMG.</t>
         </is>
       </c>
     </row>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Ngoài trạng thái [Divined Dream], gây sát thương vẫn tích được tầng [Trái Tim Phơi Bày], nhưng hiệu ứng tăng cường sẽ không hoạt động.</t>
+          <t>Ngoài trạng thái [Giấc Mộng Tiên Tri], gây sát thương vẫn tích được tầng [Trái Tim Phơi Bày], nhưng hiệu ứng tăng cường sẽ không hoạt động.</t>
         </is>
       </c>
     </row>
@@ -16847,7 +16847,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonator chủ động nhận một tầng [Sức Mạnh Thời Gian], họ sẽ nhận thêm 2 tầng nữa. Khi [Ấn Triện Thời Gian] gây sát thương, nó sẽ phục hồi 5% Dreamscape Energy.</t>
+          <t>Mỗi khi Resonator chủ động nhận một tầng [Sức Mạnh Thời Gian], họ sẽ nhận thêm 2 tầng nữa. Khi [Ấn Triện Thời Gian] gây sát thương, nó sẽ phục hồi 5% Năng Lượng Cảnh Mộng.</t>
         </is>
       </c>
     </row>
@@ -16912,7 +16912,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], mục tiêu bị Resonator chủ động tấn công sẽ bị [Time Sigil] đánh thêm một lần, gây Spectro DMG bằng 20% sát thương khi loại bỏ tầng [Temporal Power] hiện tại. Hiệu ứng này có thể kích hoạt mỗi 0.5 giây một lần.</t>
+          <t>Khi ở trong [Giấc Mộng Tiên Tri], mục tiêu bị Resonator chủ động tấn công sẽ bị [Time Sigil] đánh thêm một lần, gây DMG Spectro bằng 20% DMG khi loại bỏ tầng [Temporal Power] hiện tại. Hiệu ứng này có thể kích hoạt mỗi 0.5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Ngoài trạng thái [Divined Dream], gây sát thương vẫn tích được tầng [Năng Lượng Thời Gian]. Trong trạng thái [Divined Dream], tốc độ tấn công của tất cả Resonators trong đội tăng 30%, và tổng Sát Thương gây ra bởi [Ấn Ký Thời Gian] cũng tăng 30%.</t>
+          <t>Ngoài trạng thái [Giấc Mộng Tiên Tri], gây DMG vẫn tích được tầng [Năng Lượng Thời Gian]. Trong trạng thái [Giấc Mộng Tiên Tri], tốc độ tấn công của tất cả Resonator trong đội tăng 30%, và tổng Sát Thương gây ra bởi [Ấn Ký Thời Gian] cũng tăng 30%.</t>
         </is>
       </c>
     </row>
@@ -17042,7 +17042,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Khi Resonators chủ động gây sát thương, mục tiêu sẽ bị nhiễm 1 tầng Erosion Aero và Spectro Frazzle, kích hoạt mỗi 0.8 giây một lần. Đồng thời, tất cả Resonators trong đội sẽ nhận được Aero DMG Bonus và Spectro 8% trong 5 giây, có thể chồng chất lên đến 20 lần.</t>
+          <t>Khi Resonator chủ động gây DMG, mục tiêu sẽ bị nhiễm 1 tầng Xói Mòn Aero và Rối Loạn Spectro, kích hoạt mỗi 0.8 giây một lần. Đồng thời, tất cả Resonator trong đội sẽ nhận được Tăng Sát Thương Aero và Spectro 8% trong 5 giây, có thể chồng chất lên đến 20 lần.</t>
         </is>
       </c>
     </row>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Tổng Sát Thương gây ra lên mục tiêu bị ảnh hưởng bởi Status Tiêu Cực sẽ tăng thêm 50%. Khi ở trong [Divined Dream], hiệu ứng này tăng thêm 50% nữa.</t>
+          <t>Tổng Sát Thương gây ra lên mục tiêu bị ảnh hưởng bởi Trạng Thái Tiêu Cực sẽ tăng thêm 50%. Khi ở trong [Divined Dream], hiệu ứng này tăng thêm 50% nữa.</t>
         </is>
       </c>
     </row>
@@ -17238,8 +17238,8 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Ngoài trạng thái [Divined Dream], [Ấn Ký Erosion] vẫn có thể kích hoạt, nhưng mỗi đòn tấn công của kiếm trận chỉ gây Aero DMG bằng 120% Tấn Công.
-Trong trạng thái [Divined Dream], mỗi lần gây hiệu ứng Erosion Aero hoặc Spectro Frazzle, có 20% cơ hội gây 2 tầng hiệu ứng thay vì 1.</t>
+          <t>Ngoài trạng thái [Giấc Mộng Tiên Tri], [Ấn Ký Xói Mòn] vẫn có thể kích hoạt, nhưng mỗi đòn tấn công của kiếm trận chỉ gây Sát Thương Aero bằng 120% ATK.
+Trong trạng thái [Giấc Mộng Tiên Tri], mỗi lần gây hiệu ứng Xói Mòn Aero hoặc Rối Loạn Spectro, có 20% cơ hội gây 2 tầng hiệu ứng thay vì 1.</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators chủ động nhận khiên, họ sẽ nhận thêm một tầng [Glory]. Mỗi tầng [Glory] giờ đây tăng 1% Heavy Attack cho tất cả Resonators trong đội.</t>
+          <t>Mỗi khi Resonator chủ động nhận khiên, họ sẽ nhận thêm một tầng [Vinh Quang]. Mỗi tầng [Vinh Quang] giờ đây tăng 1% Heavy Attack cho tất cả Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -17370,8 +17370,8 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], gây Sát Thương Heavy Attack sẽ nhận được 1 tầng [Sunlight], tăng tổng Sát Thương Heavy Attack lên 5%, có thể chồng chất tối đa 15 lần. Khi đạt tối đa, tất cả tầng [Sunlight] sẽ được tiêu thụ để nhận [Burning Sun] trong 6 giây. Sau đó, không thể nhận lại [Sunlight] cho đến khi đợt [Divined Dream] này kết thúc.
-Nhận [Burning Sun] sẽ tạo một Lớp Shield tương đương 50% HP tối đa trong 10 giây và 10 tầng [Glory]. Khi ở trạng thái [Burning Sun], Crit. DMG và tổng Sát Thương Heavy Attack sẽ tăng thêm 100%.</t>
+          <t>Khi ở trong [Divined Dream], gây Sát Thương Đòn Heavy Attack sẽ nhận được 1 tầng [Sunlight], tăng tổng Sát Thương Đòn Heavy Attack lên 5%, có thể chồng chất tối đa 15 lần. Khi đạt tối đa, tất cả tầng [Sunlight] sẽ được tiêu thụ để nhận [Burning Sun] trong 6 giây. Sau đó, không thể nhận lại [Sunlight] cho đến khi đợt [Divined Dream] này kết thúc.
+Nhận [Burning Sun] sẽ tạo một Lớp Khiên tương đương 50% HP tối đa trong 10 giây và 10 tầng [Glory]. Khi ở trạng thái [Burning Sun], Crit. DMG và tổng Sát Thương Đòn Heavy Attack sẽ tăng thêm 100%.</t>
         </is>
       </c>
     </row>
@@ -17436,7 +17436,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Tất cả Resonators nhận Tấn Công bằng 2,5% lượng Shield hiện tại, tối đa 100.000 điểm Shield. Resonators mang [Glory] miễn nhiễm với gián đoạn.</t>
+          <t>Tất cả Resonator nhận ATK bằng 2,5% lượng Khiên hiện tại, tối đa 100.000 điểm Khiên. Resonator mang [Vinh Quang] miễn nhiễm với gián đoạn.</t>
         </is>
       </c>
     </row>
@@ -17502,8 +17502,8 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Khi Resonator chủ động bị tấn công trong khi đang giữ [Glory], họ kích hoạt [Retaliation]: gây Electro DMG bằng 200% Attack lên kẻ tấn công, được tính là Sát Thương Heavy Attack, và nhận Shield tương đương 2% HP tối đa trong 5 phút.
-Ngoài ra, khi Resonator chủ động gây sát thương trong khi giữ [Glory], họ cũng kích hoạt [Retaliation] lên mục tiêu, nhưng hiệu ứng này chỉ có thể xảy ra một lần mỗi giây.</t>
+          <t>Khi Resonator chủ động bị tấn công trong khi đang giữ [Glory], họ kích hoạt [Retaliation]: gây Sát Thương Electro bằng 200% ATK lên kẻ tấn công, được tính là Sát Thương Đòn Nặng, và nhận Khiên tương đương 2% HP tối đa trong 5 phút.
+Ngoài ra, khi Resonator chủ động gây DMG trong khi giữ [Glory], họ cũng kích hoạt [Retaliation] lên mục tiêu, nhưng hiệu ứng này chỉ có thể xảy ra một lần mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -17568,7 +17568,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Basic Attack triệu hồi một quả cầu lửa khi trúng mục tiêu, gây Fusion DMG. Được tăng cường trong trạng thái [Divined Dream].</t>
+          <t>Đòn Basic Attack triệu hồi một quả cầu lửa khi trúng mục tiêu, gây Sát Thương Fusion. Được tăng cường trong trạng thái [Giấc Mộng Tiên Tri].</t>
         </is>
       </c>
     </row>
@@ -17633,7 +17633,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Sử dụng Kỹ Năng Echo sẽ tạo ra một cơn lốc tại khu vực mục tiêu, gây Aero DMG. Được tăng cường trong trạng thái [Divined Dream].</t>
+          <t>Sử dụng Kỹ Năng Echo sẽ tạo ra một cơn lốc tại khu vực mục tiêu, gây Sát Thương Aero. Được tăng cường trong trạng thái [Divined Dream].</t>
         </is>
       </c>
     </row>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation triệu hồi các tia sét đánh vào các mục tiêu gần đó, gây Electro DMG. Được tăng cường khi ở trạng thái [Divined Dream].</t>
+          <t>Kích hoạt Resonance Liberation triệu hồi các tia sét đánh vào các mục tiêu gần đó, gây Sát Thương Electro. Được tăng cường khi ở trạng thái [Divined Dream].</t>
         </is>
       </c>
     </row>
@@ -17763,7 +17763,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Giới Thiệu triệu hồi Vụ Nổ Băng tấn công mục tiêu, gây Glacio DMG. Được tăng cường khi ở trạng thái [Giấc Mơ Tiên Tri].</t>
+          <t>Kích hoạt Kỹ Năng Giới Thiệu triệu hồi Vụ Nổ Băng tấn công mục tiêu, gây Sát Thương Glacio. Được tăng cường khi ở trạng thái [Giấc Mơ Tiên Tri].</t>
         </is>
       </c>
     </row>
@@ -17828,7 +17828,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], Resonator chủ động sẽ mất HP mỗi giây và gây một lượng lớn sát thương cho mục tiêu xung quanh.</t>
+          <t>Khi ở trong [Giấc Mộng Tiên Tri], Resonator chủ động sẽ mất HP mỗi giây và gây một lượng lớn DMG cho mục tiêu xung quanh.</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], gây sát thương sẽ tích lũy [Revealed Heart], tăng Crit. Rate và Crit. DMG. Tất cả các tầng sẽ mất khi [Divined Dream] kết thúc.</t>
+          <t>Khi ở trong [Divined Dream], gây DMG sẽ tích lũy [Revealed Heart], tăng Tỷ Lệ Bạo Kích và Sát Thương Bạo Kích. Tất cả các tầng sẽ mất khi [Divined Dream] kết thúc.</t>
         </is>
       </c>
     </row>
@@ -17958,7 +17958,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], gây sát thương sẽ tích lũy [Temporal Power], gây Spectro DMG khổng lồ khi [Divined Dream] kết thúc.</t>
+          <t>Khi ở trong [Divined Dream], gây DMG sẽ tích lũy [Temporal Power], gây Sát Thương Spectro khổng lồ khi [Divined Dream] kết thúc.</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], nếu tích lũy đủ tầng Aero Erosion hoặc Spectro Frazzle, Resonator sẽ triệu hồi một loạt kiếm tấn công, gây Aero DMG.</t>
+          <t>Khi ở trong [Giấc Mộng Tiên Tri], nếu tích lũy đủ tầng Aero Erosion hoặc Spectro Frazzle, Cộng Hưởng Giả sẽ triệu hồi một loạt kiếm tấn công, gây DMG Aero.</t>
         </is>
       </c>
     </row>
@@ -18088,7 +18088,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Nhận Shield sẽ tạo ra [Glory]. Khi ở trạng thái [Giấc Mơ Tiên Tri], [Glory] có thể được tiêu hao để tăng Sát Thương Heavy Attack.</t>
+          <t>Nhận Khiên sẽ tạo ra [Vinh Quang]. Khi ở trạng thái [Giấc Mơ Tiên Tri], [Vinh Quang] có thể được tiêu hao để tăng Sát Thương Đòn Heavy Attack.</t>
         </is>
       </c>
     </row>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Kích hoạt [Blaze Sigil] tăng Sát Thương Basic Attack cho tất cả Resonators và triệu hồi thêm một quả cầu lửa.</t>
+          <t>Kích hoạt [Blaze Sigil] tăng Sát Thương Basic Attack cho tất cả Resonator và triệu hồi thêm một quả cầu lửa.</t>
         </is>
       </c>
     </row>
@@ -18219,7 +18219,7 @@
       <c r="M271" t="inlineStr">
         <is>
           <t>[
-Ấn Lửa] gây tổng sát thương lớn hơn và có phạm vi rộng hơn.</t>
+Ấn Lửa] gây tổng DMG lớn hơn và có phạm vi rộng hơn.</t>
         </is>
       </c>
     </row>
@@ -18349,7 +18349,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Skill Echo gây nhiều sát thương hơn và Cooldown chiêu ngắn hơn. Khi ở trạng thái [Giấc Mơ Tiên Tri], gây sát thương Skill Echo sẽ giảm Cooldown chiêu Skill Echo của tất cả Resonators trong đội.</t>
+          <t>Kỹ năng Echo gây nhiều DMG hơn và Thời gian hồi chiêu ngắn hơn. Khi ở trạng thái [Giấc Mơ Tiên Tri], gây DMG Kỹ năng Echo sẽ giảm Thời gian hồi chiêu Kỹ năng Echo của tất cả Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], gây Sát Thương Kỹ Năng Echo sẽ tăng tổng Sát Thương của tất cả Resonators trong đội. Có thể chồng chất.</t>
+          <t>Khi ở trong [Divined Dream], gây Sát Thương Kỹ Năng Echo sẽ tăng tổng Sát Thương của tất cả Resonator trong đội. Có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -18479,7 +18479,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Kích hoạt [Huy Hiệu Bão Tố] sẽ tăng Sát Thương của tất cả Resonators trong đội và tăng thêm Sát Thương Kỹ Năng Echo. Có thể chồng chất.</t>
+          <t>Kích hoạt [Huy Hiệu Bão Tố] sẽ tăng Sát Thương của tất cả Resonator trong đội và tăng thêm Sát Thương Kỹ Năng Echo. Có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Ấn Ký Bão Tố gây tổng Sát Thương cao hơn và tạo thêm các đợt sát thương.</t>
+          <t>Ấn Ký Bão Tố gây tổng Sát Thương cao hơn và tạo thêm các đợt DMG.</t>
         </is>
       </c>
     </row>
@@ -18674,7 +18674,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Khi sử dụng Resonance Liberation, Crit. DMG tăng lên khi ở trong [Divined Dream]. Vào [Divined Dream] sẽ phục hồi đầy Resonance Energy và xóa Cooldown chiêu Resonance Liberation.</t>
+          <t>Khi sử dụng Resonance Liberation, Crit. DMG tăng lên khi ở trong [Giấc Mộng Tiên Tri]. Vào [Giấc Mộng Tiên Tri] sẽ phục hồi đầy Resonance Energy và xóa Thời gian hồi chiêu Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -18739,7 +18739,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>[Thánh Ấn Thunder] gây tổng sát thương tăng cao. Khi gây sát thương, nó hồi phục Resonance Energy cho tất cả Resonators trong đội và giảm Cooldown chiêu của Resonance Liberation.</t>
+          <t>[Thánh Ấn Sấm Sét] gây tổng DMG tăng cao. Khi gây DMG, nó hồi phục Resonance Energy cho tất cả Resonator trong đội và giảm thời gian hồi chiêu của Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -18869,7 +18869,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Mục tiêu liên tục trúng [Ấn Ký Băng Giá] sẽ chịu sát thương tăng cường và gây ít sát thương hơn.</t>
+          <t>Mục tiêu liên tục trúng [Ấn Ký Băng Giá] sẽ chịu DMG tăng cường và gây ít DMG hơn.</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Kích hoạt [Blizzard Sigil] tăng Sát Thương Resonance Skill của tất cả Resonators trong đội. Có thể chồng chất.</t>
+          <t>Kích hoạt [Blizzard Sigil] tăng Sát Thương Resonance Skill của tất cả Resonator trong đội. Có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -19000,7 +19000,7 @@
       <c r="M283" t="inlineStr">
         <is>
           <t>[
-Ấn Băng] gây tổng sát thương lớn hơn, phạm vi rộng hơn và hồi Concerto Energy cho tất cả Resonators trong đội khi trúng đích.</t>
+Ấn Băng] gây tổng DMG lớn hơn, phạm vi rộng hơn và hồi Concerto Energy cho tất cả Resonator trong đội khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -19130,7 +19130,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Mục tiêu bị ảnh hưởng bởi [Ấn Triệu Cuồng Loạn] sẽ chịu tổng sát thương cao hơn. Có thể chồng chất.</t>
+          <t>Mục tiêu bị ảnh hưởng bởi [Ấn Triệu Cuồng Loạn] sẽ chịu tổng DMG cao hơn. Có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -19195,7 +19195,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], HP tối đa của Resonator chủ động sẽ tăng liên tục. Có thể chồng tầng.</t>
+          <t>Khi ở trong [Giấc Mộng Tiên Tri], HP tối đa của Resonator chủ động sẽ tăng liên tục. Có thể chồng tầng.</t>
         </is>
       </c>
     </row>
@@ -19260,7 +19260,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], Resonator chủ động càng mất nhiều HP, cộng dồn sát thương của họ càng tăng.</t>
+          <t>Khi ở trong [Giấc Mộng Tiên Tri], Resonator chủ động càng mất nhiều HP, cộng dồn DMG của họ càng tăng.</t>
         </is>
       </c>
     </row>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], mọi Crit. Rate vượt quá 100% sẽ được chuyển đổi thành Crit. DMG bổ sung.</t>
+          <t>Khi ở trong [Divined Dream], mọi Tỷ Lệ Bạo Kích vượt quá 100% sẽ được chuyển đổi thành Sát Thương Bạo Kích bổ sung.</t>
         </is>
       </c>
     </row>
@@ -19390,7 +19390,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>[Năng Lực Thời Gian] được thu thập hiệu quả hơn. [Ấn Ký Thời Gian] sẽ hồi phục Dreamscape Energy khi gây sát thương.</t>
+          <t>[Năng Lực Thời Gian] được thu thập hiệu quả hơn. [Ấn Ký Thời Gian] sẽ hồi phục Năng Lượng Cảnh Mộng khi gây sát thương.</t>
         </is>
       </c>
     </row>
@@ -19455,7 +19455,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Khi gây sát thương trong [Divined Dream], [Ấn Triện Thời Gian] sẽ gây thêm Spectro DMG một lần.</t>
+          <t>Khi gây DMG trong [Giấc Mộng Tiên Tri], [Ấn Triện Thời Gian] sẽ gây thêm Sát Thương Spectro một lần.</t>
         </is>
       </c>
     </row>
@@ -19520,7 +19520,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>[Năng Lực Thời Gian] có thể thu được từ [Giấc Mơ Tiên Tri]. Khi ở trong [Giấc Mơ Tiên Tri], Resonators tấn công nhanh hơn, và [Ấn Ký Thời Gian] gây tổng sát thương cao hơn.</t>
+          <t>[Năng Lực Thời Gian] có thể thu được từ [Giấc Mơ Tiên Tri]. Khi ở trong [Giấc Mơ Tiên Tri], Resonator tấn công nhanh hơn, và [Ấn Ký Thời Gian] gây tổng DMG cao hơn.</t>
         </is>
       </c>
     </row>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Gây sát thương gây hiệu ứng Erosion Aero và Spectro Frazzle, đồng thời tăng Aero DMG và Spectro của tất cả Resonators trong đội.</t>
+          <t>Gây DMG gây hiệu ứng Xói Mòn Aero và Rối Loạn Spectro, đồng thời tăng Sát Thương Aero và Spectro của tất cả Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -19715,7 +19715,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Gây tổng sát thương cao hơn lên mục tiêu đang chịu [Status Tiêu Cực], cộng thêm tăng sát thương khi ở trong [Giấc Mơ Tiên Tri].</t>
+          <t>Gây tổng DMG cao hơn lên mục tiêu đang chịu [Trạng Thái Tiêu Cực], cộng thêm tăng DMG khi ở trong [Giấc Mơ Tiên Tri].</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>["Ấn Tẩm Erosion"] có thể kích hoạt ngoài ["Giấc Mơ Tiên Tri"], nhưng gây ít sát thương hơn. Khi ở trong ["Giấc Mơ Tiên Tri"], nó có thể kích hoạt thường xuyên hơn.</t>
+          <t>["Ấn Tẩm Xói Mòn"] có thể kích hoạt ngoài ["Giấc Mơ Tiên Tri"], nhưng gây ít DMG hơn. Khi ở trong ["Giấc Mơ Tiên Tri"], nó có thể kích hoạt thường xuyên hơn.</t>
         </is>
       </c>
     </row>
@@ -19845,7 +19845,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Glory có thể đạt được hiệu quả hơn và tăng Sát Thương Heavy Attack cho tất cả Resonators trong đội.</t>
+          <t>Vinh Quang có thể đạt được hiệu quả hơn và tăng Sát Thương Đòn Heavy Attack cho tất cả Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], gây Sát Thương Heavy Attack sẽ nhận được tăng Sát Thương. Sau 15 tầng, bạn sẽ bước vào trạng thái đặc biệt, tăng mạnh Crit. DMG và tổng Sát Thương Heavy Attack.</t>
+          <t>Khi ở trong [Divined Dream], gây Sát Thương Đòn Nặng sẽ nhận được tăng Sát Thương. Sau 15 tầng, bạn sẽ bước vào trạng thái đặc biệt, tăng mạnh Crit. DMG và tổng Sát Thương Đòn Nặng.</t>
         </is>
       </c>
     </row>
@@ -19975,7 +19975,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Càng tích lũy nhiều điểm Shield, chỉ số Tấn Công càng cao. [Glory] giúp miễn nhiễm với hiệu ứng gián đoạn.</t>
+          <t>Càng tích lũy nhiều điểm Khiên, chỉ số ATK càng cao. [Glory] giúp miễn nhiễm với hiệu ứng gián đoạn.</t>
         </is>
       </c>
     </row>
@@ -20040,7 +20040,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Khi nhận sát thương, tiêu hao [Glory] để phản đòn kẻ tấn công và nhận một Lớp Shield. Hiệu ứng này cũng có thể kích hoạt định kỳ khi gây sát thương.</t>
+          <t>Khi nhận sát thương, tiêu hao [Glory] để phản đòn kẻ tấn công và nhận một Lớp Khiên. Hiệu ứng này cũng có thể kích hoạt định kỳ khi gây sát thương.</t>
         </is>
       </c>
     </row>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Khoảng thời gian kích hoạt</t>
+          <t>Khoảng Cách Kích Hoạt</t>
         </is>
       </c>
     </row>
@@ -20170,7 +20170,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -20430,7 +20430,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Điều kiện kích hoạt</t>
+          <t>Điều Kiện Kích Hoạt</t>
         </is>
       </c>
     </row>
@@ -20495,7 +20495,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Số tầng</t>
+          <t>Số Lớp Chồng</t>
         </is>
       </c>
     </row>
@@ -20625,7 +20625,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Điều kiện kích hoạt</t>
+          <t>Điều Kiện Kích Hoạt</t>
         </is>
       </c>
     </row>
@@ -20690,7 +20690,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Khi Resonator chủ động gây sát thương, họ gây thêm 15% sát thương và chịu thêm 5% sát thương trong 10 giây, tối đa 5 tầng. Hiệu ứng kích hoạt mỗi 2 giây một lần.</t>
+          <t>Khi Resonator chủ động gây DMG, họ gây thêm 15% DMG và chịu thêm 5% DMG trong 10 giây, tối đa 5 tầng. Hiệu ứng kích hoạt mỗi 2 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -20755,7 +20755,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Khi Resonator chủ động gây sát thương, Tấn Công của họ tăng 15% và HP tối đa giảm 5% trong 10 giây, có thể chồng chất lên đến 5 lần. Hiệu ứng này chỉ có thể kích hoạt mỗi 2 giây một lần.</t>
+          <t>Khi Resonator chủ động gây sát thương, ATK của họ tăng 15% và HP tối đa giảm 5% trong 10 giây, có thể chồng chất lên đến 5 lần. Hiệu ứng này chỉ có thể kích hoạt mỗi 2 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -21015,7 +21015,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Khi Resonator chủ động sử dụng Resonance Liberation, tiêu hao 50% HP hiện tại để tăng Tấn Công thêm 25% trong 10 giây. Hiệu ứng này chỉ có thể kích hoạt mỗi 10 giây một lần.</t>
+          <t>Khi Resonator chủ động sử dụng Resonance Liberation, tiêu hao 50% HP hiện tại để tăng ATK thêm 25% trong 10 giây. Hiệu ứng này chỉ có thể kích hoạt mỗi 10 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -21080,7 +21080,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>ATK tăng 22,5%.</t>
+          <t>ATK tăng 22.5%.</t>
         </is>
       </c>
     </row>
@@ -21275,7 +21275,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Sát thương Basic Attack tăng thêm 22,5%.</t>
+          <t>DMG Basic Attack tăng thêm 22,5%.</t>
         </is>
       </c>
     </row>
@@ -21340,7 +21340,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Sát thương Heavy Attack tăng thêm 22,5%.</t>
+          <t>DMG Heavy Attack tăng thêm 22,5%.</t>
         </is>
       </c>
     </row>
@@ -21470,7 +21470,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Sát thương Resonance Liberation tăng 22,5%.</t>
+          <t>DMG Resonance Liberation tăng 22,5%.</t>
         </is>
       </c>
     </row>
@@ -21600,7 +21600,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Basic Attack trúng mục tiêu sẽ hồi 10 điểm Dreamscape Energy, kích hoạt mỗi 0.5 giây một lần.</t>
+          <t>Basic Attack trúng mục tiêu sẽ hồi 10 điểm Năng Lượng Cảnh Mộng, kích hoạt mỗi 0.5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -21795,7 +21795,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>HP tối đa của tất cả Resonators trong đội được nhân đôi nhưng bị khóa.</t>
+          <t>HP tối đa của tất cả Resonator trong đội được nhân đôi nhưng bị khóa.</t>
         </is>
       </c>
     </row>
@@ -21860,7 +21860,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Tấn Công của tất cả Resonators trong đội được nhân đôi nhưng bị khóa.</t>
+          <t>ATK của tất cả Resonator trong đội được nhân đôi nhưng bị khóa.</t>
         </is>
       </c>
     </row>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Khi Resonator chủ động gây sát thương, họ gây thêm 25% sát thương và chịu thêm 5% sát thương trong 10 giây, tối đa 3 tầng. Hiệu ứng kích hoạt mỗi 2 giây một lần. Tất cả các tầng sẽ mất khi thời gian kết thúc.</t>
+          <t>Khi Resonator chủ động gây DMG, họ gây thêm 25% DMG và chịu thêm 5% DMG trong 10 giây, tối đa 3 tầng. Hiệu ứng kích hoạt mỗi 2 giây một lần. Tất cả các tầng sẽ mất khi thời gian kết thúc.</t>
         </is>
       </c>
     </row>
@@ -21990,7 +21990,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Khi Resonator chủ động gây sát thương, Tấn Công của họ tăng 25% và HP tối đa giảm 5% trong 10 giây, có thể chồng chất lên đến 3 lần. Hiệu ứng này chỉ có thể kích hoạt mỗi 2 giây một lần. Tất cả các tầng chồng chất sẽ bị xóa khi thời gian hiệu lực kết thúc.</t>
+          <t>Khi Resonator chủ động gây sát thương, ATK của họ tăng 25% và HP tối đa giảm 5% trong 10 giây, có thể chồng chất lên đến 3 lần. Hiệu ứng này chỉ có thể kích hoạt mỗi 2 giây một lần. Tất cả các tầng chồng chất sẽ bị xóa khi thời gian hiệu lực kết thúc.</t>
         </is>
       </c>
     </row>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Khi Resonator chủ động chịu Sát Thương, Tấn Công tăng thêm 1 cho mỗi 10 HP bị mất, kéo dài trong 10 giây.</t>
+          <t>Khi Resonator chủ động chịu Sát Thương, ATK tăng thêm 1 cho mỗi 10 HP bị mất, kéo dài trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -22510,7 +22510,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Sát thương Basic Attack tăng thêm 45%.</t>
+          <t>DMG Basic Attack tăng thêm 45%.</t>
         </is>
       </c>
     </row>
@@ -22575,7 +22575,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Sát thương Heavy Attack tăng thêm 45%.</t>
+          <t>DMG Heavy Attack tăng thêm 45%.</t>
         </is>
       </c>
     </row>
@@ -22705,7 +22705,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Sát thương Resonance Liberation tăng 45%.</t>
+          <t>DMG Resonance Liberation tăng 45%.</t>
         </is>
       </c>
     </row>
@@ -22770,7 +22770,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Tốc độ Attack cơ bản tăng 20%.</t>
+          <t>Tốc độ Tấn Công cơ bản tăng 20%.</t>
         </is>
       </c>
     </row>
@@ -22835,7 +22835,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Basic Attack trúng mục tiêu sẽ hồi 20 điểm Dreamscape Energy, kích hoạt mỗi 0.5 giây một lần.</t>
+          <t>Basic Attack trúng mục tiêu sẽ hồi 20 điểm Năng Lượng Cảnh Mộng, kích hoạt mỗi 0.5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -22900,7 +22900,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Thời gian [Divined Dream] giảm 25%, nhưng tất cả Resonators trong đội nhận thêm 75% Tăng Sát Thương.</t>
+          <t>Thời gian [Divined Dream] giảm 25%, nhưng tất cả Resonator trong đội nhận thêm 75% Tăng Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -22965,7 +22965,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Thời gian [Divined Dream] trở thành vĩnh viễn, nhưng tất cả Resonators trong đội gây ít hơn 30% tổng sát thương.</t>
+          <t>Thời gian [Divined Dream] trở thành vĩnh viễn, nhưng tất cả Resonator trong đội gây ít hơn 30% tổng DMG.</t>
         </is>
       </c>
     </row>
@@ -23225,7 +23225,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Sát thương Basic Attack tăng thêm 67,5%.</t>
+          <t>DMG Basic Attack tăng thêm 67,5%.</t>
         </is>
       </c>
     </row>
@@ -23290,7 +23290,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Sát thương Heavy Attack tăng thêm 67,5%.</t>
+          <t>DMG Heavy Attack tăng thêm 67,5%.</t>
         </is>
       </c>
     </row>
@@ -23420,7 +23420,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Sát thương Resonance Liberation tăng 67,5%.</t>
+          <t>DMG Resonance Liberation tăng 67,5%.</t>
         </is>
       </c>
     </row>
@@ -23485,7 +23485,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Basic Attack trúng mục tiêu sẽ hồi 50 điểm Dreamscape Energy, kích hoạt mỗi 0.5 giây một lần.</t>
+          <t>Basic Attack trúng mục tiêu sẽ hồi 50 điểm Năng Lượng Cảnh Mộng, kích hoạt mỗi 0.5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -23550,7 +23550,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Khi Resonator chủ động gây sát thương, họ gây thêm một chút sát thương và chịu thêm một chút sát thương. Có thể chồng tầng.</t>
+          <t>Khi Resonator chủ động gây DMG, họ gây thêm một chút DMG và chịu thêm một chút DMG. Có thể chồng tầng.</t>
         </is>
       </c>
     </row>
@@ -23615,7 +23615,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Khi Resonator chủ động gây sát thương, Tấn Công của họ tăng nhẹ và HP tối đa giảm đi. Có thể chồng chất.</t>
+          <t>Khi Resonator chủ động gây sát thương, ATK của họ tăng nhẹ và HP tối đa giảm đi. Có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -23810,7 +23810,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Nhận Dreamscape Energy khi tiêu diệt mục tiêu.</t>
+          <t>Nhận Năng Lượng Cảnh Mộng khi tiêu diệt mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -23875,7 +23875,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation tiêu hao HP để tăng Tấn Công.</t>
+          <t>Kích hoạt Giải Cứu Cộng Hưởng tiêu hao HP để tăng ATK.</t>
         </is>
       </c>
     </row>
@@ -24005,7 +24005,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Max HP tăng nhẹ.</t>
+          <t>HP tối đa tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -24135,7 +24135,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Sát thương Basic Attack tăng nhẹ.</t>
+          <t>DMG Basic Attack tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Sát thương Heavy Attack tăng nhẹ.</t>
+          <t>DMG Heavy Attack tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -24330,7 +24330,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Sát thương Resonance Liberation tăng nhẹ.</t>
+          <t>DMG Resonance Liberation tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -24395,7 +24395,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Tốc độ Attack cơ bản tăng nhẹ.</t>
+          <t>Tốc độ Tấn Công cơ bản tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -24460,7 +24460,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Basic Attack trúng mục tiêu sẽ hồi một lượng nhỏ Dreamscape Energy.</t>
+          <t>Basic Attack trúng mục tiêu sẽ hồi một lượng nhỏ Năng Lượng Cảnh Mộng.</t>
         </is>
       </c>
     </row>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Gây DMG sẽ phục hồi HP.</t>
+          <t>Gây sát thương sẽ hồi phục HP.</t>
         </is>
       </c>
     </row>
@@ -24655,7 +24655,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>HP tối đa của tất cả Resonators trong đội được nhân đôi nhưng bị khóa.</t>
+          <t>HP tối đa của tất cả Resonator trong đội được nhân đôi nhưng bị khóa.</t>
         </is>
       </c>
     </row>
@@ -24720,7 +24720,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Tấn Công của tất cả Resonators trong đội được nhân đôi nhưng bị khóa.</t>
+          <t>ATK của tất cả Resonator trong đội được nhân đôi nhưng bị khóa.</t>
         </is>
       </c>
     </row>
@@ -24785,7 +24785,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Khi Resonator chủ động gây sát thương, họ gây thêm sát thương và chịu thêm sát thương. Có thể chồng tầng.</t>
+          <t>Khi Resonator chủ động gây DMG, họ gây thêm DMG và chịu thêm DMG. Có thể chồng tầng.</t>
         </is>
       </c>
     </row>
@@ -24850,7 +24850,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Khi Resonator chủ động gây sát thương, Tấn Công của họ tăng lên và HP tối đa giảm đi. Có thể chồng chất.</t>
+          <t>Khi Resonator chủ động gây sát thương, ATK của họ tăng lên và HP tối đa giảm đi. Có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -25110,7 +25110,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Khi Resonator chủ động chịu Sát Thương, Tấn Công của họ tăng dựa trên lượng HP đã mất.</t>
+          <t>Khi Resonator chủ động chịu Sát Thương, ATK của họ tăng dựa trên lượng HP đã mất.</t>
         </is>
       </c>
     </row>
@@ -25175,7 +25175,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>ATK tăng vừa.</t>
+          <t>ATK tăng vừa phải.</t>
         </is>
       </c>
     </row>
@@ -25240,7 +25240,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Max HP tăng vừa.</t>
+          <t>HP tối đa tăng vừa phải.</t>
         </is>
       </c>
     </row>
@@ -25305,7 +25305,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Crit. Rate tăng vừa.</t>
+          <t>Crit. Rate tăng vừa phải.</t>
         </is>
       </c>
     </row>
@@ -25370,7 +25370,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Sát thương Basic Attack tăng ở mức vừa phải.</t>
+          <t>DMG Basic Attack tăng ở mức vừa phải.</t>
         </is>
       </c>
     </row>
@@ -25435,7 +25435,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Sát thương Heavy Attack tăng vừa phải.</t>
+          <t>DMG Heavy Attack tăng vừa phải.</t>
         </is>
       </c>
     </row>
@@ -25565,7 +25565,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Sát thương Resonance Liberation tăng vừa phải.</t>
+          <t>DMG Resonance Liberation tăng vừa phải.</t>
         </is>
       </c>
     </row>
@@ -25630,7 +25630,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Tốc độ Attack cơ bản tăng vừa phải.</t>
+          <t>Tốc độ Tấn Công cơ bản tăng vừa phải.</t>
         </is>
       </c>
     </row>
@@ -25695,7 +25695,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Basic Attack trúng mục tiêu sẽ hồi một phần Dreamscape Energy.</t>
+          <t>Basic Attack trúng mục tiêu sẽ hồi một phần Năng Lượng Cảnh Mộng.</t>
         </is>
       </c>
     </row>
@@ -25760,7 +25760,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Thời gian [Divined Dream] bị rút ngắn, nhưng sát thương của tất cả Resonators trong đội được tăng cường.</t>
+          <t>Thời gian [Divined Dream] bị rút ngắn, nhưng sát thương của tất cả Resonator trong đội được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Thời gian [Divined Dream] trở thành vĩnh viễn, nhưng tất cả Resonators trong đội gây ít hơn tổng sát thương.</t>
+          <t>Thời gian [Divined Dream] trở thành vĩnh viễn, nhưng tất cả Resonator trong đội gây ít hơn tổng DMG.</t>
         </is>
       </c>
     </row>
@@ -25955,7 +25955,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Max HP tăng mạnh.</t>
+          <t>HP tối đa tăng mạnh.</t>
         </is>
       </c>
     </row>
@@ -26085,7 +26085,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Sát thương Basic Attack tăng mạnh</t>
+          <t>DMG Basic Attack tăng mạnh</t>
         </is>
       </c>
     </row>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack tăng mạnh.</t>
+          <t>Sát Thương Đòn Heavy Attack tăng mạnh.</t>
         </is>
       </c>
     </row>
@@ -26345,7 +26345,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Basic Attack trúng mục tiêu sẽ hồi một lượng lớn Dreamscape Energy.</t>
+          <t>Basic Attack trúng mục tiêu sẽ hồi một lượng lớn Năng Lượng Cảnh Mộng.</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>&lt;color=#c25757&gt;Đã đạt cấp tối đa. Vui lòng tăng Giai đoạn SOL3 của bạn&lt;/color&gt;</t>
+          <t>&lt;color=#c25757&gt;Đã đạt cấp tối đa. Hãy nâng cấp Giai Đoạn SOL3 của bạn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26670,7 +26670,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Vật liệu nâng cấp kỹ năng</t>
+          <t>Vật Liệu Nâng Cấp Kỹ Năng</t>
         </is>
       </c>
     </row>
@@ -26866,8 +26866,8 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Toàn bộ Resonators trong đội nhận &lt;color=#ffd12f&gt;30% Spectro DMG Bonus&lt;/color&gt;.
-Gây &lt;color=#ffd12f&gt;Spectro DMG&lt;/color&gt; sẽ nhận thêm Dreamscape Energy.</t>
+          <t>Toàn bộ Resonator trong đội nhận &lt;color=#ffd12f&gt;Tăng 30% Sát Thương Spectro&lt;/color&gt;.
+Gây &lt;color=#ffd12f&gt;Sát Thương Spectro&lt;/color&gt; sẽ nhận thêm Năng Lượng Cảnh Mộng.</t>
         </is>
       </c>
     </row>
@@ -26933,8 +26933,8 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Toàn bộ Resonators trong đội nhận &lt;color=#ffd12f&gt;30% Havoc DMG Bonus&lt;/color&gt;.
-Gây &lt;color=#ffd12f&gt;Havoc DMG&lt;/color&gt; sẽ nhận thêm Dreamscape Energy.</t>
+          <t>Toàn bộ Resonator trong đội nhận &lt;color=#ffd12f&gt;Tăng 30% Sát Thương Havoc&lt;/color&gt;.
+Gây &lt;color=#ffd12f&gt;Sát Thương Havoc&lt;/color&gt; sẽ nhận thêm Năng Lượng Cảnh Mộng.</t>
         </is>
       </c>
     </row>
@@ -27000,8 +27000,8 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Toàn bộ Resonators trong đội nhận &lt;color=#ffd12f&gt;30% Fusion DMG Bonus&lt;/color&gt;.
-Gây &lt;color=#ffd12f&gt;Fusion DMG&lt;/color&gt; sẽ nhận thêm Dreamscape Energy.</t>
+          <t>Toàn bộ Resonator trong đội nhận &lt;color=#ffd12f&gt;Tăng 30% Sát Thương Fusion&lt;/color&gt;.
+Gây &lt;color=#ffd12f&gt;Sát Thương Fusion&lt;/color&gt; sẽ nhận thêm Năng Lượng Cảnh Mộng.</t>
         </is>
       </c>
     </row>
@@ -27067,8 +27067,8 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>* Tất cả Resonators trong đội nhận &lt;color=#ffd12f&gt;30% Electro DMG Bonus&lt;/color&gt;.
-* Gây &lt;color=#ffd12f&gt;Electro DMG&lt;/color&gt; sẽ nhận thêm Năng Lượng Giấc Mơ.</t>
+          <t>* Tất cả Resonator trong đội nhận &lt;color=#ffd12f&gt;Tăng 30% Sát Thương Electro&lt;/color&gt;.
+* Gây &lt;color=#ffd12f&gt;Sát Thương Electro&lt;/color&gt; sẽ nhận thêm Năng Lượng Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -27134,8 +27134,8 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Toàn bộ Resonators trong đội nhận &lt;color=#ffd12f&gt;30% Glacio DMG Bonus&lt;/color&gt;.
-Gây &lt;color=#ffd12f&gt;Glacio DMG&lt;/color&gt; sẽ nhận thêm Dreamscape Energy.</t>
+          <t>Toàn bộ Resonator trong đội nhận &lt;color=#ffd12f&gt;Tăng 30% Sát Thương Glacio&lt;/color&gt;.
+Gây &lt;color=#ffd12f&gt;Sát Thương Glacio&lt;/color&gt; sẽ nhận thêm Năng Lượng Cảnh Mộng.</t>
         </is>
       </c>
     </row>
@@ -27201,8 +27201,8 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>* Tất cả Resonators trong đội nhận &lt;color=#ffd12f&gt;30% Aero DMG Bonus&lt;/color&gt;.
-* Gây &lt;color=#ffd12f&gt;Aero DMG&lt;/color&gt; sẽ nhận thêm Năng Lượng Giấc Mơ.</t>
+          <t>* Tất cả Resonator trong đội nhận &lt;color=#ffd12f&gt;Tăng 30% Sát Thương Aero&lt;/color&gt;.
+* Gây &lt;color=#ffd12f&gt;Sát Thương Aero&lt;/color&gt; sẽ nhận thêm Năng Lượng Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -27401,10 +27401,10 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Report thường kỳ của Fractsidus sau khi kiểm tra Nhà máy Fabricatorium.
+          <t>Báo cáo thường kỳ của Fractsidus sau khi kiểm tra Nhà máy Fabricatorium.
 1. Sản xuất Echo thông thường tại tất cả các khu vực của Nhà máy Fabricatorium đều hoạt động bình thường, các thành viên của Hội đang giám sát chặt chẽ. Không phát hiện bất thường.
 2. Quá trình mở rộng lực lượng của Fenrico và đội quân riêng vẫn diễn ra suôn sẻ theo thỏa thuận hợp tác giữa hai bên.
-3. Việc mở rộng Lost Beyond gặp trục trặc. Đại Giám Sát đã ở trạng thái Overclock liên tục trong 15 ngày, gây ra các vụ nổ nhỏ do khả năng Resonance ảnh hưởng đến sự ổn định không gian. Công tác ổn định đã bắt đầu, việc mở rộng sẽ tiếp tục sau khi Đại Giám Sát được nghỉ ngơi đầy đủ.
+3. Việc mở rộng Lost Beyond gặp trục trặc. Đại Giám Sát đã ở trạng thái Overclock liên tục trong 15 ngày, gây ra các vụ nổ nhỏ do khả năng Cộng Hưởng ảnh hưởng đến sự ổn định không gian. Công tác ổn định đã bắt đầu, việc mở rộng sẽ tiếp tục sau khi Đại Giám Sát được nghỉ ngơi đầy đủ.
 4. Lần thử nghiệm cuối cùng sử dụng liều vi lượng sức mạnh của Threnodian để hợp nhất Reverberation của con người và Tacet Discord đã được tiến hành, tỷ lệ thành công vẫn như thường lệ.</t>
         </is>
       </c>
@@ -27470,7 +27470,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Kích Hoạt Hoàn Toàn Chuỗi Resonance Augusta</t>
+          <t>Kích Hoạt Hoàn Toàn Resonance Chain Augusta</t>
         </is>
       </c>
     </row>
@@ -27535,7 +27535,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Kích hoạt đầy đủ Resonance Chain của Iuno</t>
+          <t>Kích hoạt hoàn toàn Resonance Chain của Iuno</t>
         </is>
       </c>
     </row>
@@ -27670,12 +27670,12 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>[Trích từ Report Sức khỏe Thể chất Thí sinh Agon █████]
-Name: Augusta
-Lịch sử Resonance của thí sinh này bắt đầu từ thời thơ ấu, gần như trùng với tuổi đời của cô. Có giả thuyết cho rằng cô là một &lt;te href=850068&gt;Congenital Resonator&lt;/te&gt;.
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của thí sinh Augusta nằm ở mu bàn tay trái. Khi kích hoạt, cô có thể tạo ra và điều khiển từ trường trong bán kính khoảng mười mét, tập trung quanh bản thân. Khi làm chủ được Forte của mình, cô có thể tự do kiểm soát và biến đổi các vật liệu như sắt, coban và niken. Tuy nhiên, dựa trên lời khai cá nhân và dữ liệu thử nghiệm, Forte của cô dường như đã đạt đến giới hạn phát triển, với bán kính mười mét là ngưỡng thực tế cao nhất.
+          <t>[Trích từ Báo cáo Sức khỏe Thể chất Thí sinh Agon █████]
+Tên: Augusta
+Lịch sử Cộng Hưởng của thí sinh này bắt đầu từ thời thơ ấu, gần như trùng với tuổi đời của cô. Có giả thuyết cho rằng cô là một &lt;te href=850068&gt;Resonator Bẩm Sinh&lt;/te&gt;.
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của thí sinh Augusta nằm ở mu bàn tay trái. Khi kích hoạt, cô có thể tạo ra và điều khiển từ trường trong bán kính khoảng mười mét, tập trung quanh bản thân. Khi làm chủ được Forte của mình, cô có thể tự do kiểm soát và biến đổi các vật liệu như sắt, coban và niken. Tuy nhiên, dựa trên lời khai cá nhân và dữ liệu thử nghiệm, Forte của cô dường như đã đạt đến giới hạn phát triển, với bán kính mười mét là ngưỡng thực tế cao nhất.
 &lt;i&gt;"Một Resonator Bẩm Sinh hiếm có, nhưng Forte của cô ta chẳng mang lại lợi thế gì đáng kể trong chiến đấu, thậm chí có thể gọi là 'tầm thường'. Để một người như cô ta nổi bật trong Agon? Cũng khó như mặt trời mọc lúc nửa đêm. Chỉ là ảo tưởng." —Ghi chú của nhân viên y tế&lt;/i&gt;
-&lt;i&gt;Tacet Mark in hằn trên mu bàn tay từ thuở ấu thơ vừa là món quà từ trên trời ban xuống, vừa là trò đùa tàn nhẫn. Forte yếu ớt từng như xiềng xích trói buộc cô, nhưng giờ đây, cô đã từ lâu đập tan những gông cùm ấy. Từng bước, cô leo lên bậc thềm ngai vàng, chứng minh cho tất cả thấy rằng ngay cả kẻ sinh ra từ cát bụi cũng có thể tỏa sáng rực rỡ như mặt trời thiêu đốt.&lt;/i&gt;</t>
+&lt;i&gt;Dấu Tacet in hằn trên mu bàn tay từ thuở ấu thơ vừa là món quà từ trên trời ban xuống, vừa là trò đùa tàn nhẫn. Forte yếu ớt từng như xiềng xích trói buộc cô, nhưng giờ đây, cô đã từ lâu đập tan những gông cùm ấy. Từng bước, cô leo lên bậc thềm ngai vàng, chứng minh cho tất cả thấy rằng ngay cả kẻ sinh ra từ cát bụi cũng có thể tỏa sáng rực rỡ như mặt trời thiêu đốt.&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -27745,11 +27745,11 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>["Trích từ &lt;te href=850152&gt;Priestess&lt;/te&gt;, Tetragon Temple]
-Mục này ghi chép về Tư Tế thứ 127 của Tetragon Temple, được biết đến với tên Iu▇.
-Nàng sinh ra vào đêm trăng khuyết. Là một &lt;te href=850068&gt;Congenital Resonator&lt;/te&gt;, đôi mắt nàng được cho là chứa đựng sức mạnh để ▇▇▇▇.
-Tacet Mark của nàng nằm trên mu bàn chân trái. Khi kích hoạt năng lực Resonance, ▇▇ cấu trúc năng lượng mang hình dáng các pha trăng hiện ra xung quanh, và mái tóc nàng trở nên trong suốt, tỏa ra ánh sáng dịu dàng gần như không thể phân biệt với ánh trăng thật.
-Phân tích phổ Resonance cho thấy Forte của nàng trùng khớp một cách kỳ lạ với tần số tự nhiên của mặt trăng, thể hiện sự điều biến pha liên tục. Đáng chú ý, ba năm trước, Forte của nàng dường như đã ▇▇▇▇. Nó có khả năng An▇ và Mani▇, cho phép nàng biến ánh trăng thành những mũi tên rắn chắc, có thể phát hiện những quái vật bị đánh dấu ẩn náu trong &lt;te href=851023&gt;Dark Tide&lt;/te&gt;.
+          <t>["Trích từ &lt;te href=850152&gt;Biên Niên Sử Tư Tế&lt;/te&gt;, Đền Tetragon]
+Mục này ghi chép về Tư Tế thứ 127 của Đền Tetragon, được biết đến với tên Iu▇.
+Nàng sinh ra vào đêm trăng khuyết. Là một &lt;te href=850068&gt;Resonator Bẩm Sinh&lt;/te&gt;, đôi mắt nàng được cho là chứa đựng sức mạnh để ▇▇▇▇.
+Dấu Tacet của nàng nằm trên mu bàn chân trái. Khi kích hoạt năng lực Cộng Hưởng, ▇▇ cấu trúc năng lượng mang hình dáng các pha trăng hiện ra xung quanh, và mái tóc nàng trở nên trong suốt, tỏa ra ánh sáng dịu dàng gần như không thể phân biệt với ánh trăng thật.
+Phân tích phổ Cộng Hưởng cho thấy Forte của nàng trùng khớp một cách kỳ lạ với tần số tự nhiên của mặt trăng, thể hiện sự điều biến pha liên tục. Đáng chú ý, ba năm trước, Forte của nàng dường như đã ▇▇▇▇. Nó có khả năng An▇ và Mani▇, cho phép nàng biến ánh trăng thành những mũi tên rắn chắc, có thể phát hiện những quái vật bị đánh dấu ẩn náu trong &lt;te href=851023&gt;Thủy Triều Bóng Tối&lt;/te&gt;.
 &lt;i&gt;Khi chúng tôi lưu trữ mục này, Bà Lillibet đã yêu cầu xác minh nhiều lần. Kỳ lạ thay, không ai trong chúng tôi nhớ được ai đã viết nó. Và còn kỳ lạ hơn, dường như không ai nhớ đến Tư Tế được miêu tả ở đây. Liệu một Tư Tế quyền năng như nàng có thực sự tồn tại? Bằng cách nào đó, bản ghi chép đột ngột này như thể được viết bằng chính ánh trăng!&lt;/i&gt;</t>
         </is>
       </c>
@@ -27846,7 +27846,7 @@
 "Đùa à? Đó là Ephor Magno đấy! Ở Septimont này, ai chẳng biết ông ấy."
 "Ephor..."
 Nấp trong bóng tối góc phố, Augusta cắn miếng bánh mì khô cuối cùng, đôi mắt dán chặt vào bóng dáng cao lớn đang diễn thuyết giữa quảng trường. Ông ta trông ngoài ba mươi, gương mặt như tạc từ đá cẩm thạch, nhưng lại dịu dàng bởi nụ cười ấm áp, cởi mở. Khi giọng nói lên đến cao trào, ông dang rộng đôi tay. Đám đông vỡ òa trong tiếng vỗ tay như sấm.
-Một nhà vô địch bất bại của các Agon công cộng. Một thiên tài đấu sĩ hiếm có trong đời. Ông đã hạ gục bảy con Corrosaurus trên cao nguyên Sanguis và trở về, mình nhuốm máu rồng. Người ta gọi ông là "Kẻ Sát Dragon". Thời ấy, những chiến công của ông vang dội khắp Septimont.
+Một nhà vô địch bất bại của các Agon công cộng. Một thiên tài đấu sĩ hiếm có trong đời. Ông đã hạ gục bảy con Corrosaurus trên cao nguyên Sanguis và trở về, mình nhuốm máu rồng. Người ta gọi ông là "Kẻ Sát Rồng". Thời ấy, những chiến công của ông vang dội khắp Septimont.
 Ông lắng nghe dân chúng. Không bao giờ từ chối lời cầu xin. Cai trị không tham lam. Một Ephor được chọn bởi ý nguyện của quần chúng. Nhiều người tin rằng ông sẽ trở thành Anh Hùng của các Anh Hùng như lời tiên tri.
 Với Augusta, danh hiệu đó luôn xa vời và không thể chạm tới. Nhưng lần đầu tiên, cô thấy một người có thể thực sự vươn tới nó.
 Một ngọn lửa bùng lên trong lồng ngực cô. Những chiến công mà cô từng cho là phóng đại, những truyền thuyết lay động tâm hồn... hóa ra có người đã thực sự sống trong thời đại của cô. Điều đó có nghĩa giấc mơ của cô không chỉ là ảo tưởng. Nó có thể nằm trong tầm tay.
@@ -27855,20 +27855,20 @@
 Không lâu sau, Augusta đứng đối diện với chính người đàn ông ấy, những câu hỏi vẫn nặng trĩu trong lòng.
 "Chúc mừng cô gái trẻ. Cô đã nhận được sự phù hộ của Arsinosa. Cô sẽ được tôn vinh là Nhà Vô Địch mới."
 Trên bục trao huy chương, Augusta đối mặt với Magno khi ông chuẩn bị gắn huy chương lên ngực cô. Nhưng đằng sau nụ cười gượng gạo, cô thấy đôi mắt u ám vì mệt mỏi.
-Người hùng mà cô từng mường tượng không còn đứng đó. Ngọn lửa cũng không còn. Chiến binh từng được tung hô là Kẻ Sát Dragon đã biến mất.
+Người hùng mà cô từng mường tượng không còn đứng đó. Ngọn lửa cũng không còn. Chiến binh từng được tung hô là Kẻ Sát Rồng đã biến mất.
 Augusta im lặng nhận vinh dự. Rồi ngay trước khi bước đi, cô thì thầm đủ để chỉ ông nghe thấy—
 "Những truyền thuyết về ông... có bao giờ là sự thật không?"
 Ông trả lời bằng nụ cười im lặng.
 Một thời gian sau, một đấu sĩ vô danh xuất hiện trong hầm đấu ngầm. Ông ta đội mũ trụ che kín mặt, bộ giáp đen như đá obsidian. Ông chiến đấu như kẻ không còn gì để mất. Chỉ tìm kiếm những đối thủ mạnh nhất. Không phô trương. Không danh dự. Ông không chiến đấu vì vinh quang. Ông chiến đấu như thể đang săn đuổi cái chết.
-"The Nameless" tích lũy chiến thắng với tốc độ kinh hoàng, nhanh chóng thu hút sự chú ý của Augusta. Dù đã đăng quang Nhà Vô Địch, cô vẫn chấp nhận lời thách đấu của ông.
+"Kẻ Vô Danh" tích lũy chiến thắng với tốc độ kinh hoàng, nhanh chóng thu hút sự chú ý của Augusta. Dù đã đăng quang Nhà Vô Địch, cô vẫn chấp nhận lời thách đấu của ông.
 Khi lưỡi kiếm của họ giao nhau, cô nhận ra. Dù có đội mũ trụ, nó không thể che giấu đôi mắt u ám, kiệt quệ ấy.
 Cô không biết tại sao một Ephor được tôn kính, một anh hùng không còn gì để chứng minh, lại xuống tận bóng tối để chiến đấu trong lồng máu. Nhưng trong khoảnh khắc đó, chẳng điều gì quan trọng. Điều duy nhất quan trọng là đối thủ mạnh mẽ trước mặt cô và cách đánh bại ông ta.
-Thép va chạm, hết lần này đến lần khác. Không ai nhường ai. Để phá vỡ thế bế tắc, kiếm của The Nameless loé lên tia điện. Những tia sét đỏ rực nhảy múa trên lưỡi kiếm. Sét hóa thành vũ khí. Đòn tấn công tối thượng, nhằm kết liễu tất cả.
+Thép va chạm, hết lần này đến lần khác. Không ai nhường ai. Để phá vỡ thế bế tắc, kiếm của Kẻ Vô Danh loé lên tia điện. Những tia sét đỏ rực nhảy múa trên lưỡi kiếm. Sét hóa thành vũ khí. Đòn tấn công tối thượng, nhằm kết liễu tất cả.
 Và trong ánh chớp lóa mắt ấy, Augusta nhìn thấy. Huyền thoại. Chiến binh của cao nguyên Sanguis, tay cầm sấm sét, xé toang mây đen và tuyệt vọng để mang hy vọng đến cho những người phía sau.
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; trên mu bàn tay cô bừng sáng. Cô không thể triệu hồi sấm sét như ông. Forte của cô chỉ là tiếng thì thầm so với tiếng gầm của ông. Nhưng dù vậy—
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; trên mu bàn tay cô bừng sáng. Cô không thể triệu hồi sấm sét như ông. Forte của cô chỉ là tiếng thì thầm so với tiếng gầm của ông. Nhưng dù vậy—
 Tia lửa kháng cự yếu ớt ấy vẫn làm lệch đi tia sét, chỉ một chút.
 Và trong khoảng khắc mở ấy, Augusta tấn công bằng tất cả sức lực. Một đòn cuối cùng.
-Sau ngày hôm đó, The Nameless biến mất khỏi hầm đấu. Với thế giới, đó chỉ là một trong vô số chiến thắng của Augusta. Không ai nhận ra rằng một huyền thoại đã lặng lẽ khép lại.
+Sau ngày hôm đó, Kẻ Vô Danh biến mất khỏi hầm đấu. Với thế giới, đó chỉ là một trong vô số chiến thắng của Augusta. Không ai nhận ra rằng một huyền thoại đã lặng lẽ khép lại.
 Một thời gian sau, vào một ngày bình thường như bao ngày khác, Augusta nhận được một lá thư. Một lời mời viết tay từ Cung điện Ephor.</t>
         </is>
       </c>
@@ -28001,7 +28001,7 @@
       <c r="M420" t="inlineStr">
         <is>
           <t>&lt;color=#41aefb&gt;&lt;te href=800013&gt;Isomer Bolt&lt;/te&gt;&lt;/color&gt; hấp thụ &lt;color=#917701&gt;&lt;te href=800016&gt;Glittering Ray&lt;/te&gt;&lt;/color&gt; và giờ định kỳ phóng các tia xuyên qua kẻ địch.
-Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800026&gt;Bullet Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800026&gt;Vũ Khí Đạn&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -28068,7 +28068,7 @@
       <c r="M421" t="inlineStr">
         <is>
           <t>&lt;color=#41aefb&gt;&lt;te href=800013&gt;Isomer Bolt&lt;/te&gt;&lt;/color&gt; hấp thụ &lt;color=#be6245&gt;&lt;te href=800025&gt;Explosive Omen&lt;/te&gt;&lt;/color&gt; và giờ đây sẽ phát nổ định kỳ trong khu vực mục tiêu, gây thêm Sát Thương Khu Vực.
-Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800026&gt;Bullet Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800026&gt;Vũ Khí Đạn&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -28135,7 +28135,7 @@
       <c r="M422" t="inlineStr">
         <is>
           <t>Tầm ảnh hưởng và Hệ Số Sát Thương của &lt;color=#be6245&gt;&lt;te href=800022&gt;Blazing Stars&lt;/te&gt;&lt;/color&gt; được tăng lên.
-Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800026&gt;Bullet Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800026&gt;Vũ Khí Đạn&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -28202,7 +28202,7 @@
       <c r="M423" t="inlineStr">
         <is>
           <t>Tích tụ năng lượng. Tầm bắn và Hệ số Sát Thương của &lt;color=#be6245&gt;&lt;te href=800022&gt;Blazing Stars&lt;/te&gt;&lt;/color&gt; sẽ được tăng cường thêm.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800026&gt;Bullet Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800026&gt;Vũ khí đạn đạo&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -28268,8 +28268,8 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>&lt;color=#be6245&gt;&lt;te href=800022&gt;Blazing Star&lt;/te&gt;&lt;/color&gt; hấp thụ &lt;color=#9c5884&gt;&lt;te href=800015&gt;Sanguine Wheel&lt;/te&gt;&lt;/color&gt; và giờ đây bắn ra nhiều &lt;color=#be6245&gt;&lt;te href=800022&gt;Blazing Stars&lt;/te&gt;&lt;/color&gt;, gây sát thương lên kẻ địch xung quanh khi va chạm.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800026&gt;Bullet Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+          <t>&lt;color=#be6245&gt;&lt;te href=800022&gt;Blazing Star&lt;/te&gt;&lt;/color&gt; hấp thụ &lt;color=#9c5884&gt;&lt;te href=800015&gt;Sanguine Wheel&lt;/te&gt;&lt;/color&gt; và giờ đây bắn ra nhiều &lt;color=#be6245&gt;&lt;te href=800022&gt;Blazing Star&lt;/te&gt;&lt;/color&gt;, gây sát thương lên kẻ địch xung quanh khi va chạm.
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800026&gt;Vũ Khí Đạn&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -28336,7 +28336,7 @@
       <c r="M425" t="inlineStr">
         <is>
           <t>&lt;color=#be6245&gt;&lt;te href=800022&gt;Blazing Star&lt;/te&gt;&lt;/color&gt; hấp thụ &lt;color=#9c5884&gt;&lt;te href=800023&gt;Rampant Fire&lt;/te&gt;&lt;/color&gt; và giờ đây tạo ra vùng lửa tại điểm va chạm, thiêu đốt liên tục kẻ địch bên trong.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800026&gt;Bullet Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800026&gt;Vũ Khí Đạn&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -28401,7 +28401,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=#c49e55&gt;&lt;te href=800021&gt;Zephyr Symphony&lt;/te&gt;&lt;/color&gt;, liên tục gây Aero DMG cho kẻ địch xung quanh, tăng Sát Thương Ciaccona phải chịu và giảm Movement Speed của cô ấy.</t>
+          <t>Kích hoạt &lt;color=#c49e55&gt;&lt;te href=800021&gt;Khúc Giao Hưởng Gió&lt;/te&gt;&lt;/color&gt;, liên tục gây Sát Thương Aero cho kẻ địch xung quanh, tăng Sát Thương Ciaccona phải chịu và giảm Tốc Độ Di Chuyển của cô ấy.</t>
         </is>
       </c>
     </row>
@@ -28466,7 +28466,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Hiệu ứng của Active Skill &lt;color=#c49e55&gt;&lt;te href=800021&gt;Zephyr Symphony&lt;/te&gt;&lt;/color&gt; được tăng cường.</t>
+          <t>Hiệu ứng của Kỹ Năng Chủ Động &lt;color=#c49e55&gt;&lt;te href=800021&gt;Zephyr Symphony&lt;/te&gt;&lt;/color&gt; được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -28531,7 +28531,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Hiệu ứng của Active Skill &lt;color=#c49e55&gt;&lt;te href=800021&gt;Zephyr Symphony&lt;/te&gt;&lt;/color&gt; được tăng cường thêm.</t>
+          <t>Hiệu ứng của Kỹ Năng Chủ Động &lt;color=#c49e55&gt;&lt;te href=800021&gt;Zephyr Symphony&lt;/te&gt;&lt;/color&gt; được tăng cường thêm.</t>
         </is>
       </c>
     </row>
@@ -28596,7 +28596,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Triệu hồi &lt;color=#c49e55&gt;&lt;te href=800018&gt;Breeze Breaker&lt;/te&gt;&lt;/color&gt;, gây Aero DMG lên kẻ địch xung quanh. Trong thời gian ngắn, Movement Speed tăng lên, và Rover nhận thêm Sát Thương dựa trên phần thưởng Movement Speed.</t>
+          <t>Triệu hồi &lt;color=#c49e55&gt;&lt;te href=800018&gt;Breeze Breaker&lt;/te&gt;&lt;/color&gt;, gây Sát Thương Aero lên kẻ địch xung quanh. Trong thời gian ngắn, Tốc Độ Di Chuyển tăng lên, và Rover nhận thêm Sát Thương dựa trên phần thưởng Tốc Độ Di Chuyển.</t>
         </is>
       </c>
     </row>
@@ -28661,7 +28661,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Hiệu ứng của Active Skill &lt;color=#c49e55&gt;&lt;te href=800018&gt;Breeze Breaker&lt;/te&gt;&lt;/color&gt; được tăng cường.</t>
+          <t>Hiệu ứng của Kỹ Năng Chủ Động &lt;color=#c49e55&gt;&lt;te href=800018&gt;Breeze Breaker&lt;/te&gt;&lt;/color&gt; được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -28726,7 +28726,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Hiệu ứng của Active Skill &lt;color=#c49e55&gt;&lt;te href=800018&gt;Breeze Breaker&lt;/te&gt;&lt;/color&gt; được tăng cường thêm.</t>
+          <t>Hiệu ứng của Kỹ Năng Chủ Động &lt;color=#c49e55&gt;&lt;te href=800018&gt;Breeze Breaker&lt;/te&gt;&lt;/color&gt; được tăng cường thêm.</t>
         </is>
       </c>
     </row>
@@ -28923,9 +28923,9 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Gây sát thương hoặc tiêu diệt kẻ địch sẽ hồi phục Ember. 
+          <t>Gây DMG hoặc tiêu diệt kẻ địch sẽ hồi phục Ember. 
 Trạng thái Sóng Cháy kích hoạt khi Ember đầy, kéo dài trong 30 giây. Trong thời gian này, Sát Thương gây ra tăng thêm 60%. 
-Khi bị kỹ năng của Resonator đánh trúng, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;Tune Break DMG&lt;/color&gt; rồi thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;.</t>
+Khi bị kỹ năng của Resonator đánh trúng, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;Sát Thương Phá Nhịp&lt;/color&gt; rồi thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28995,9 +28995,9 @@
       <c r="M435" t="inlineStr">
         <is>
           <t>Tấn Công tăng 30%. 
-Gây sát thương hoặc đánh bại kẻ địch sẽ hồi Phục Hỏa. 
+Gây DMG hoặc đánh bại kẻ địch sẽ hồi Phục Hỏa. 
 Trạng thái Sóng Lửa Bùng Cháy kích hoạt khi Phục Hỏa đầy, kéo dài 30 giây. Trong thời gian này, Tấn Công tăng 60%. 
-Khi bị kỹ năng của Resonator đánh trúng, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;Tune Break DMG&lt;/color&gt; rồi thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mistune&lt;/color&gt;. 
+Khi bị kỹ năng của Resonator đánh trúng, kẻ địch trong trạng thái &lt;color=#ffb04a&gt;Mê Tấu&lt;/color&gt; sẽ chịu một lần &lt;color=#ffb04a&gt;Sát Thương Phá Tấu&lt;/color&gt; rồi thoát khỏi trạng thái &lt;color=#ffb04a&gt;Mê Tấu&lt;/color&gt;. 
 Tất cả Token có thể sử dụng không giới hạn trong Vực Vô Tận.</t>
         </is>
       </c>
@@ -29063,7 +29063,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Đồng Hồ Forte</t>
+          <t>Đồng Hồ Mạch Năng Lực</t>
         </is>
       </c>
     </row>
@@ -29193,7 +29193,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Tấn Công +9%.</t>
+          <t>ATK +9%.</t>
         </is>
       </c>
     </row>
@@ -29258,7 +29258,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Giảm DMG +8%.</t>
+          <t>Giảm Sát Thương +8%</t>
         </is>
       </c>
     </row>
@@ -29323,7 +29323,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>DMG Bonus +7,5%.</t>
+          <t>Thêm Sát Thương +7.5%</t>
         </is>
       </c>
     </row>
@@ -29390,8 +29390,8 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Hiệu ứng Rampage:
-Khi Resonator tiêu diệt 0/60/150 kẻ địch, sẽ bước vào Cấp Rampage 1/2/3.
+          <t>Hiệu ứng Cuồng Nộ:
+Khi Resonator tiêu diệt 0/60/150 kẻ địch, sẽ bước vào Cấp Cuồng Nộ 1/2/3.
 Trong trạng thái này, tất cả Mô-đun Tăng Cường thu thập được sẽ được tính toán. Nếu không tiêu diệt thêm kẻ địch trong khoảng thời gian nhất định, hiệu ứng sẽ mất đi. Thoát khỏi trạng thái ở Cấp 2/3 sẽ nhận thêm 10/15% tổng số Mô-đun Tăng Cường đã thu thập.</t>
         </is>
       </c>
@@ -29457,7 +29457,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>HP Regen +12%.</t>
+          <t>Hồi HP +12%.</t>
         </is>
       </c>
     </row>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>STA tối đa &amp; Phục hồi +15%.</t>
+          <t>STA và phục hồi tăng tối đa +15%</t>
         </is>
       </c>
     </row>
@@ -29782,7 +29782,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Total Sát Thương gây ra cho kẻ địch hạng Elite &amp; Overlord tăng 25%.</t>
+          <t>Tổng Sát Thương gây ra cho kẻ địch hạng Elite &amp; Overlord tăng 25%.</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Nhận ngay 500 Mô-đun Tăng Cường, nhưng giá trong Shop sẽ tăng vĩnh viễn 15%.</t>
+          <t>Nhận ngay 500 Mô-đun Tăng Cường, nhưng giá trong Cửa Hàng sẽ tăng vĩnh viễn 15%.</t>
         </is>
       </c>
     </row>
@@ -30042,7 +30042,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Khi nhặt Mô-đun Tăng Cường, gây Sát Thương Physical bằng 20% Tấn Công của Resonator lên kẻ địch xung quanh, kích hoạt mỗi 0.2 giây.</t>
+          <t>Khi nhặt Mô-đun Tăng Cường, gây Sát Thương Vật Lý bằng 20% ATK của Resonator lên kẻ địch xung quanh, kích hoạt mỗi 0.2 giây.</t>
         </is>
       </c>
     </row>
@@ -30367,7 +30367,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Sát thương nhận vào tăng 100%, Tấn Công tăng 50%.</t>
+          <t>DMG nhận vào tăng 100%, Tấn Công tăng 50%.</t>
         </is>
       </c>
     </row>
@@ -30432,7 +30432,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Tất cả kẻ địch chịu ít hơn 40% sát thương, nhưng số lượng Mô-đun Tăng Cường nhận được tăng gấp đôi.</t>
+          <t>Tất cả kẻ địch chịu ít hơn 40% DMG, nhưng số lượng Module Tăng Cường nhận được tăng gấp đôi.</t>
         </is>
       </c>
     </row>
@@ -30497,7 +30497,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>HP của tất cả kẻ địch giảm 30%, nhưng số lượng Mô-đun Tăng Cường nhận được cũng giảm 30%.</t>
+          <t>HP của tất cả kẻ địch giảm 30%, nhưng số lượng Module Tăng Cường nhận được cũng giảm 30%.</t>
         </is>
       </c>
     </row>
@@ -30627,7 +30627,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Tấn Công giảm 25%, nhưng HP tối đa tăng 100%.</t>
+          <t>ATK giảm 25%, nhưng HP tối đa tăng 100%.</t>
         </is>
       </c>
     </row>
@@ -30692,7 +30692,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>HP tối đa giảm 50% và hiệu quả hồi máu giảm 100%, nhưng tổng sát thương gây ra tăng 50%.</t>
+          <t>HP tối đa giảm 50% và hiệu quả hồi máu giảm 100%, nhưng tổng DMG gây ra tăng 50%.</t>
         </is>
       </c>
     </row>
@@ -30757,7 +30757,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Movement Speed giảm 75%, nhưng HP Tối Đa tăng 50% và tổng Sát Thương gây ra tăng 50%</t>
+          <t>Tốc Độ Di Chuyển giảm 75%, nhưng HP Tối Đa tăng 50% và tổng Sát Thương gây ra tăng 50%</t>
         </is>
       </c>
     </row>
@@ -30887,7 +30887,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Nhận ngay thẻ nâng cấp Crit. Rate, xác suất nhận thẻ nâng cấp Crit. Rate tăng thêm 10%.</t>
+          <t>Nhận ngay thẻ nâng cấp Tỷ Lệ Bạo Kích, xác suất nhận thẻ nâng cấp Tỷ Lệ Bạo Kích tăng thêm 10%.</t>
         </is>
       </c>
     </row>
@@ -30952,7 +30952,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Nhận ngay thẻ nâng cấp Tấn Công, đồng thời tỷ lệ nhận thẻ nâng cấp Tấn Công tăng thêm 10%.</t>
+          <t>Nhận ngay thẻ nâng cấp ATK, đồng thời tỷ lệ nhận thẻ nâng cấp ATK tăng thêm 10%.</t>
         </is>
       </c>
     </row>
@@ -31017,7 +31017,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Trong Cơn Thịnh Nộ Cấp 2/3, tổng sát thương gây ra tăng thêm 15/30%.</t>
+          <t>Trong Cơn Thịnh Nộ Cấp 2/3, tổng DMG gây ra tăng thêm 15/30%.</t>
         </is>
       </c>
     </row>
@@ -31082,7 +31082,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Thời gian duy trì Cấp Rampage 1/2/3 kéo dài thêm 2/2/1 giây.</t>
+          <t>Thời gian duy trì Cấp Cuồng Nộ 1/2/3 kéo dài thêm 2/2/1 giây.</t>
         </is>
       </c>
     </row>
@@ -31147,7 +31147,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Tăng 40% Total Sát Thương lên kẻ địch ở xa, nhưng giảm 30% đối với kẻ địch ở gần.</t>
+          <t>Tăng 40% Tổng Sát Thương lên kẻ địch ở xa, nhưng giảm 30% đối với kẻ địch ở gần.</t>
         </is>
       </c>
     </row>
@@ -31212,7 +31212,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Tăng 40% Total Sát Thương lên kẻ địch ở gần, nhưng giảm 30% đối với kẻ địch ở xa.</t>
+          <t>Tăng 40% Tổng Sát Thương lên kẻ địch ở gần, nhưng giảm 30% đối với kẻ địch ở xa.</t>
         </is>
       </c>
     </row>
@@ -31277,7 +31277,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Total Sát Thương gây ra cho tất cả kẻ địch tăng 30%, nhưng Resonator chịu thêm 50% Sát Thương.</t>
+          <t>Tổng Sát Thương gây ra cho tất cả kẻ địch tăng 30%, nhưng Resonator chịu thêm 50% Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Tăng 30% Total Sát Thương lên kẻ địch hạng Elite và Overlord, nhưng giảm 30% đối với kẻ địch hạng Common.</t>
+          <t>Tăng 30% Tổng Sát Thương lên kẻ địch hạng Elite và Overlord, nhưng giảm 30% đối với kẻ địch hạng Common.</t>
         </is>
       </c>
     </row>
@@ -31407,7 +31407,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Tổng Sát Thương của &lt;color=#c49e55&gt;&lt;te href=800029&gt;Morph Weapons&lt;/te&gt;&lt;/color&gt; tăng thêm 40%.</t>
+          <t>Tổng Sát Thương của &lt;color=#c49e55&gt;&lt;te href=800029&gt;Vũ Khí Biến Hình&lt;/te&gt;&lt;/color&gt; tăng thêm 40%.</t>
         </is>
       </c>
     </row>
@@ -31472,7 +31472,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Crit. Rate của &lt;color=#c49e55&gt;&lt;te href=800029&gt;Morph Weapons&lt;/te&gt;&lt;/color&gt; đối với kẻ địch xung quanh tăng thêm 30%.</t>
+          <t>Crit. Rate của &lt;color=#c49e55&gt;&lt;te href=800029&gt;Vũ Khí Biến Hình&lt;/te&gt;&lt;/color&gt; đối với kẻ địch xung quanh tăng thêm 30%.</t>
         </is>
       </c>
     </row>
@@ -31537,7 +31537,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;&lt;te href=800029&gt;Morph Weapons&lt;/te&gt;&lt;/color&gt; bỏ qua 75% Phòng Ngự khi gây Sát Thương lên kẻ địch hạng Elite và Overlord.</t>
+          <t>&lt;color=#c49e55&gt;&lt;te href=800029&gt;Vũ Khí Biến Hình&lt;/te&gt;&lt;/color&gt; bỏ qua 75% Phòng Ngự khi gây Sát Thương lên kẻ địch hạng Elite và Overlord.</t>
         </is>
       </c>
     </row>
@@ -31602,7 +31602,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;&lt;te href=800026&gt;Bullet Weapons&lt;/te&gt;&lt;/color&gt; tăng 40% tổng Sát Thương.</t>
+          <t>&lt;color=#c49e55&gt;&lt;te href=800026&gt;Vũ Khí Súng&lt;/te&gt;&lt;/color&gt; tăng 40% tổng Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -31667,7 +31667,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;&lt;te href=800026&gt;Bullet Weapons&lt;/te&gt;&lt;/color&gt; tăng 1% Attack Speed trong 5 giây mỗi khi gây sát thương, tối đa 40 lần chồng chất.</t>
+          <t>&lt;color=#c49e55&gt;&lt;te href=800026&gt;Vũ Khí Súng&lt;/te&gt;&lt;/color&gt; tăng 1% Tốc Độ Tấn Công trong 5 giây mỗi khi gây sát thương, tối đa 40 lần chồng chất.</t>
         </is>
       </c>
     </row>
@@ -31732,7 +31732,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;&lt;te href=800026&gt;Bullet Weapons&lt;/te&gt;&lt;/color&gt; tăng 60% Crit. DMG đối với kẻ địch ở xa.</t>
+          <t>&lt;color=#c49e55&gt;&lt;te href=800026&gt;Vũ Khí Súng&lt;/te&gt;&lt;/color&gt; tăng 60% Crit. DMG đối với kẻ địch ở xa.</t>
         </is>
       </c>
     </row>
@@ -31797,7 +31797,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Tổng Sát Thương của &lt;color=#c49e55&gt;&lt;te href=800028&gt;Beam Weapons&lt;/te&gt;&lt;/color&gt; tăng thêm 40%.</t>
+          <t>Tổng Sát Thương của &lt;color=#c49e55&gt;&lt;te href=800028&gt;Vũ Khí Tia&lt;/te&gt;&lt;/color&gt; tăng thêm 40%.</t>
         </is>
       </c>
     </row>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;&lt;te href=800028&gt;Beam Weapons&lt;/te&gt;&lt;/color&gt; tăng 4% Sát Thương trong 15 giây mỗi khi gây sát thương lên kẻ địch, tối đa 10 lần chồng chất. Đồng thời tăng 16% Movement Speed.</t>
+          <t>&lt;color=#c49e55&gt;&lt;te href=800028&gt;Vũ Khí Tia&lt;/te&gt;&lt;/color&gt; tăng 4% Sát Thương trong 15 giây mỗi khi gây DMG lên kẻ địch, tối đa 10 lần chồng chất. Đồng thời tăng 16% Tốc Độ Di Chuyển.</t>
         </is>
       </c>
     </row>
@@ -31927,7 +31927,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;&lt;te href=800028&gt;Beam Weapons&lt;/te&gt;&lt;/color&gt; tăng 20% Sát Thương đối với kẻ địch gần, và thêm 30% đối với kẻ địch ở xa.</t>
+          <t>&lt;color=#c49e55&gt;&lt;te href=800028&gt;Vũ Khí Tia&lt;/te&gt;&lt;/color&gt; tăng 20% Sát Thương đối với kẻ địch gần, và thêm 30% đối với kẻ địch ở xa.</t>
         </is>
       </c>
     </row>
@@ -31992,7 +31992,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;&lt;te href=800027&gt;Summon Weapons&lt;/te&gt;&lt;/color&gt; tăng 40% Sát Thương.</t>
+          <t>&lt;color=#c49e55&gt;&lt;te href=800027&gt;Vũ Khí Triệu Hồi&lt;/te&gt;&lt;/color&gt; tăng 40% Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#c49e55&gt;&lt;te href=800027&gt;Summon Weapons&lt;/te&gt;&lt;/color&gt; gây sát thương lên kẻ địch bị làm chậm, Kháng Sát Thương toàn thuộc tính của chúng sẽ giảm 40% trong 4 giây.</t>
+          <t>Khi &lt;color=#c49e55&gt;&lt;te href=800027&gt;Vũ Khí Triệu Hồi&lt;/te&gt;&lt;/color&gt; gây DMG lên kẻ địch bị làm chậm, Kháng Sát Thương toàn thuộc tính của chúng sẽ giảm 40% trong 4 giây.</t>
         </is>
       </c>
     </row>
@@ -32122,7 +32122,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Mỗi lần &lt;color=#c49e55&gt;&lt;te href=800027&gt;Summon Weapons&lt;/te&gt;&lt;/color&gt; gây sát thương, kẻ địch trúng đòn sẽ chịu thêm 1% sát thương trong 6 giây, tối đa cộng dồn 50 lần.</t>
+          <t>Mỗi lần &lt;color=#c49e55&gt;&lt;te href=800027&gt;Vũ Khí Triệu Hồi&lt;/te&gt;&lt;/color&gt; gây DMG, kẻ địch trúng đòn sẽ chịu thêm 1% DMG trong 6 giây, tối đa cộng dồn 50 lần.</t>
         </is>
       </c>
     </row>
@@ -32187,7 +32187,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Spectro DMG tăng 50%.</t>
+          <t>Sát Thương Spectro tăng 50%.</t>
         </is>
       </c>
     </row>
@@ -32252,7 +32252,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Havoc DMG tăng thêm 50%.</t>
+          <t>Sát Thương Havoc tăng thêm 50%.</t>
         </is>
       </c>
     </row>
@@ -32317,7 +32317,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Aero DMG tăng thêm 50%.</t>
+          <t>Sát Thương Aero tăng thêm 50%.</t>
         </is>
       </c>
     </row>
@@ -32382,7 +32382,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus lên 50%.</t>
+          <t>Tăng Sát Thương Fusion lên 50%.</t>
         </is>
       </c>
     </row>
@@ -32447,7 +32447,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Glacio DMG tăng thêm 50%.</t>
+          <t>DMG Glacio tăng thêm 50%.</t>
         </is>
       </c>
     </row>
@@ -32512,7 +32512,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Electro DMG tăng thêm 50%.</t>
+          <t>Sát Thương Electro tăng thêm 50%.</t>
         </is>
       </c>
     </row>
@@ -32839,7 +32839,7 @@
       <c r="M494" t="inlineStr">
         <is>
           <t>- Tăng tần suất xuất hiện kẻ địch cận chiến hạng Phổ Thông.
-- Lần đầu xuất hiện &lt;color=HighlightB&gt;Flautist&lt;/color&gt; cận chiến hạng Elite.</t>
+- Lần đầu xuất hiện &lt;color=HighlightB&gt;Flautist&lt;/color&gt; cận chiến hạng Tinh Anh.</t>
         </is>
       </c>
     </row>
@@ -32971,9 +32971,9 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[&lt;te href=800027&gt;Summon Weapon&lt;/te&gt;]&lt;/color&gt;
-Tỷ lệ triệu hồi và hệ số sát thương của &lt;color=#2c9366&gt;&lt;te href=800024&gt;Feilian Shocks&lt;/te&gt;&lt;/color&gt; được tăng lên.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800027&gt;Summon Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+          <t>&lt;color=#c49e55&gt;[&lt;te href=800027&gt;Vũ Khí Triệu Hồi&lt;/te&gt;]&lt;/color&gt;
+Tỷ lệ triệu hồi và hệ số DMG của &lt;color=#2c9366&gt;&lt;te href=800024&gt;Feilian Shocks&lt;/te&gt;&lt;/color&gt; được tăng lên.
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800027&gt;Vũ Khí Triệu Hồi&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -33040,7 +33040,7 @@
       <c r="M497" t="inlineStr">
         <is>
           <t>Nếm thử cơn thịnh nộ của bầy đàn nào. Phạm vi tấn công, tốc độ triệu hồi và Hệ Số Sát Thương của &lt;color=#2c9366&gt;&lt;te href=800024&gt;Feilian Shocks&lt;/te&gt;&lt;/color&gt; được tăng cường thêm.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800027&gt;Summon Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800027&gt;Vũ Khí Triệu Hồi&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -33106,8 +33106,8 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>&lt;color=#2c9366&gt;&lt;te href=800024&gt;Feilian Shock&lt;/te&gt;&lt;/color&gt; hấp thụ &lt;color=#be6245&gt;&lt;te href=800025&gt;Explosive Omen&lt;/te&gt;&lt;/color&gt; và giờ triệu hồi rồi kích nổ nhiều &lt;color=#be6245&gt;&lt;te href=800025&gt;Explosive Omens&lt;/te&gt;&lt;/color&gt; để tấn công kẻ địch xung quanh.
-Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800027&gt;Summon Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+          <t>&lt;color=#2c9366&gt;&lt;te href=800024&gt;Feilian Shock&lt;/te&gt;&lt;/color&gt; hấp thụ &lt;color=#be6245&gt;&lt;te href=800025&gt;Explosive Omen&lt;/te&gt;&lt;/color&gt; và giờ triệu hồi rồi kích nổ nhiều &lt;color=#be6245&gt;&lt;te href=800025&gt;Explosive Omen&lt;/te&gt;&lt;/color&gt; để tấn công kẻ địch xung quanh.
+Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800027&gt;Vũ Khí Triệu Hồi&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -33173,8 +33173,8 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>&lt;color=#2c9366&gt;&lt;te href=800024&gt;Feilian Shock&lt;/te&gt;&lt;/color&gt; hấp thụ &lt;color=#9c5884&gt;&lt;te href=800015&gt;Sanguine Wheel&lt;/te&gt;&lt;/color&gt; và giờ phóng nhiều &lt;color=#9c5884&gt;&lt;te href=800015&gt;Sanguine Wheels&lt;/te&gt;&lt;/color&gt; cùng lúc, gây thêm Sát Thương mỗi lần tấn công.
-Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800027&gt;Summon Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+          <t>&lt;color=#2c9366&gt;&lt;te href=800024&gt;Feilian Shock&lt;/te&gt;&lt;/color&gt; hấp thụ &lt;color=#9c5884&gt;&lt;te href=800015&gt;Sanguine Wheel&lt;/te&gt;&lt;/color&gt; và giờ phóng nhiều &lt;color=#9c5884&gt;&lt;te href=800015&gt;Sanguine Wheel&lt;/te&gt;&lt;/color&gt; cùng lúc, gây thêm Sát Thương mỗi lần tấn công.
+Phân loại: &lt;color=#c49e55&gt;[&lt;te href=800027&gt;Vũ Khí Triệu Hồi&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -33241,7 +33241,7 @@
       <c r="M500" t="inlineStr">
         <is>
           <t>Phóng &lt;color=#2c9366&gt;&lt;te href=800014&gt;Zenith Windblade&lt;/te&gt;&lt;/color&gt; xuyên thủng kẻ địch.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800028&gt;Beam Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800028&gt;Vũ khí tia&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -33308,9 +33308,9 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[&lt;te href=800028&gt;Beam Weapon&lt;/te&gt;]&lt;/color&gt;
-Tầm tấn công và hệ số sát thương của &lt;color=#2c9366&gt;&lt;te href=800014&gt;Zenith Windblades&lt;/te&gt;&lt;/color&gt; được tăng lên.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800028&gt;Beam Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+          <t>&lt;color=#c49e55&gt;[&lt;te href=800028&gt;Vũ Khí Tia&lt;/te&gt;]&lt;/color&gt;
+Tầm tấn công và hệ số DMG của &lt;color=#2c9366&gt;&lt;te href=800014&gt;Zenith Windblades&lt;/te&gt;&lt;/color&gt; được tăng lên.
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800028&gt;Vũ Khí Tia&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
